--- a/research/traditional_assets/database/data/norway/norway_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_packaging_container.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07251485179629544</v>
+        <v>0.07239041912234359</v>
       </c>
       <c r="C2">
-        <v>1444.142424890065</v>
+        <v>1432.088330353292</v>
       </c>
       <c r="D2">
-        <v>1420.342424890065</v>
+        <v>1423.354330353292</v>
       </c>
       <c r="E2">
-        <v>-436.8</v>
+        <v>-421.734</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15.066</v>
       </c>
       <c r="G2">
         <v>23.8</v>
@@ -1445,28 +1445,28 @@
         <v>125.25</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7578197999999999</v>
       </c>
       <c r="N2">
-        <v>125.25</v>
+        <v>124.4921802</v>
       </c>
       <c r="O2">
-        <v>27.555</v>
+        <v>27.388279644</v>
       </c>
       <c r="P2">
-        <v>97.69499999999999</v>
+        <v>97.10390055600001</v>
       </c>
       <c r="Q2">
-        <v>166.695</v>
+        <v>166.103900556</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07251485179629544</v>
+        <v>0.0727253324468117</v>
       </c>
       <c r="T2">
-        <v>0.616971173124606</v>
+        <v>0.6218321581249817</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>165.2767584061541</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07239041912234359</v>
+        <v>0.07226598644839173</v>
       </c>
       <c r="C3">
-        <v>1432.088330353292</v>
+        <v>1420.047036746711</v>
       </c>
       <c r="D3">
-        <v>1423.354330353292</v>
+        <v>1426.379036746712</v>
       </c>
       <c r="E3">
-        <v>-421.734</v>
+        <v>-406.6679999999999</v>
       </c>
       <c r="F3">
-        <v>15.066</v>
+        <v>30.132</v>
       </c>
       <c r="G3">
         <v>23.8</v>
@@ -1527,28 +1527,28 @@
         <v>125.25</v>
       </c>
       <c r="M3">
-        <v>0.7578197999999999</v>
+        <v>1.5156396</v>
       </c>
       <c r="N3">
-        <v>124.4921802</v>
+        <v>123.7343604</v>
       </c>
       <c r="O3">
-        <v>27.388279644</v>
+        <v>27.221559288</v>
       </c>
       <c r="P3">
-        <v>97.10390055600001</v>
+        <v>96.51280111200001</v>
       </c>
       <c r="Q3">
-        <v>166.103900556</v>
+        <v>165.512801112</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0727253324468117</v>
+        <v>0.07294010862080789</v>
       </c>
       <c r="T3">
-        <v>0.6218321581249817</v>
+        <v>0.6267923469008753</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>165.2767584061541</v>
+        <v>82.63837920307705</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07226598644839173</v>
+        <v>0.07214155377443988</v>
       </c>
       <c r="C4">
-        <v>1420.047036746711</v>
+        <v>1408.01862585216</v>
       </c>
       <c r="D4">
-        <v>1426.379036746712</v>
+        <v>1429.41662585216</v>
       </c>
       <c r="E4">
-        <v>-406.6679999999999</v>
+        <v>-391.602</v>
       </c>
       <c r="F4">
-        <v>30.132</v>
+        <v>45.19799999999999</v>
       </c>
       <c r="G4">
         <v>23.8</v>
@@ -1609,28 +1609,28 @@
         <v>125.25</v>
       </c>
       <c r="M4">
-        <v>1.5156396</v>
+        <v>2.2734594</v>
       </c>
       <c r="N4">
-        <v>123.7343604</v>
+        <v>122.9765406</v>
       </c>
       <c r="O4">
-        <v>27.221559288</v>
+        <v>27.054838932</v>
       </c>
       <c r="P4">
-        <v>96.51280111200001</v>
+        <v>95.921701668</v>
       </c>
       <c r="Q4">
-        <v>165.512801112</v>
+        <v>164.921701668</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07294010862080789</v>
+        <v>0.07315931316952566</v>
       </c>
       <c r="T4">
-        <v>0.6267923469008753</v>
+        <v>0.6318548076102924</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>82.63837920307705</v>
+        <v>55.09225280205137</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07214155377443988</v>
+        <v>0.07201712110048804</v>
       </c>
       <c r="C5">
-        <v>1408.01862585216</v>
+        <v>1396.003180149607</v>
       </c>
       <c r="D5">
-        <v>1429.41662585216</v>
+        <v>1432.467180149607</v>
       </c>
       <c r="E5">
-        <v>-391.602</v>
+        <v>-376.5359999999999</v>
       </c>
       <c r="F5">
-        <v>45.19799999999999</v>
+        <v>60.264</v>
       </c>
       <c r="G5">
         <v>23.8</v>
@@ -1691,28 +1691,28 @@
         <v>125.25</v>
       </c>
       <c r="M5">
-        <v>2.2734594</v>
+        <v>3.0312792</v>
       </c>
       <c r="N5">
-        <v>122.9765406</v>
+        <v>122.2187208</v>
       </c>
       <c r="O5">
-        <v>27.054838932</v>
+        <v>26.888118576</v>
       </c>
       <c r="P5">
-        <v>95.921701668</v>
+        <v>95.330602224</v>
       </c>
       <c r="Q5">
-        <v>164.921701668</v>
+        <v>164.330602224</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07315931316952566</v>
+        <v>0.07338308447967504</v>
       </c>
       <c r="T5">
-        <v>0.6318548076102924</v>
+        <v>0.6370227362511557</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>55.09225280205137</v>
+        <v>41.31918960153853</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07201712110048804</v>
+        <v>0.07189268842653618</v>
       </c>
       <c r="C6">
-        <v>1396.003180149607</v>
+        <v>1384.000782824616</v>
       </c>
       <c r="D6">
-        <v>1432.467180149607</v>
+        <v>1435.530782824616</v>
       </c>
       <c r="E6">
-        <v>-376.5359999999999</v>
+        <v>-361.47</v>
       </c>
       <c r="F6">
-        <v>60.264</v>
+        <v>75.33</v>
       </c>
       <c r="G6">
         <v>23.8</v>
@@ -1773,28 +1773,28 @@
         <v>125.25</v>
       </c>
       <c r="M6">
-        <v>3.0312792</v>
+        <v>3.789099</v>
       </c>
       <c r="N6">
-        <v>122.2187208</v>
+        <v>121.460901</v>
       </c>
       <c r="O6">
-        <v>26.888118576</v>
+        <v>26.72139822</v>
       </c>
       <c r="P6">
-        <v>95.330602224</v>
+        <v>94.73950278000001</v>
       </c>
       <c r="Q6">
-        <v>164.330602224</v>
+        <v>163.73950278</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07338308447967504</v>
+        <v>0.07361156676477493</v>
       </c>
       <c r="T6">
-        <v>0.6370227362511557</v>
+        <v>0.6422994633897214</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>41.31918960153853</v>
+        <v>33.05535168123082</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07189268842653618</v>
+        <v>0.07176825575258433</v>
       </c>
       <c r="C7">
-        <v>1384.000782824616</v>
+        <v>1372.011517775909</v>
       </c>
       <c r="D7">
-        <v>1435.530782824616</v>
+        <v>1438.607517775909</v>
       </c>
       <c r="E7">
-        <v>-361.47</v>
+        <v>-346.4039999999999</v>
       </c>
       <c r="F7">
-        <v>75.33</v>
+        <v>90.396</v>
       </c>
       <c r="G7">
         <v>23.8</v>
@@ -1855,28 +1855,28 @@
         <v>125.25</v>
       </c>
       <c r="M7">
-        <v>3.789099</v>
+        <v>4.546918799999999</v>
       </c>
       <c r="N7">
-        <v>121.460901</v>
+        <v>120.7030812</v>
       </c>
       <c r="O7">
-        <v>26.72139822</v>
+        <v>26.554677864</v>
       </c>
       <c r="P7">
-        <v>94.73950278000001</v>
+        <v>94.148403336</v>
       </c>
       <c r="Q7">
-        <v>163.73950278</v>
+        <v>163.148403336</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07361156676477493</v>
+        <v>0.07384491037508972</v>
       </c>
       <c r="T7">
-        <v>0.6422994633897214</v>
+        <v>0.6476884613184694</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.05535168123082</v>
+        <v>27.54612640102568</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07176825575258433</v>
+        <v>0.07164382307863248</v>
       </c>
       <c r="C8">
-        <v>1372.011517775909</v>
+        <v>1360.035469623024</v>
       </c>
       <c r="D8">
-        <v>1438.607517775909</v>
+        <v>1441.697469623024</v>
       </c>
       <c r="E8">
-        <v>-346.404</v>
+        <v>-331.338</v>
       </c>
       <c r="F8">
-        <v>90.39599999999999</v>
+        <v>105.462</v>
       </c>
       <c r="G8">
         <v>23.8</v>
@@ -1937,28 +1937,28 @@
         <v>125.25</v>
       </c>
       <c r="M8">
-        <v>4.546918799999999</v>
+        <v>5.304738599999999</v>
       </c>
       <c r="N8">
-        <v>120.7030812</v>
+        <v>119.9452614</v>
       </c>
       <c r="O8">
-        <v>26.554677864</v>
+        <v>26.387957508</v>
       </c>
       <c r="P8">
-        <v>94.148403336</v>
+        <v>93.55730389200001</v>
       </c>
       <c r="Q8">
-        <v>163.148403336</v>
+        <v>162.557303892</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07384491037508972</v>
+        <v>0.07408327212756181</v>
       </c>
       <c r="T8">
-        <v>0.6476884613184694</v>
+        <v>0.6531933516757925</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.54612640102568</v>
+        <v>23.61096548659344</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07164382307863248</v>
+        <v>0.07151939040468062</v>
       </c>
       <c r="C9">
-        <v>1360.035469623024</v>
+        <v>1348.072723714074</v>
       </c>
       <c r="D9">
-        <v>1441.697469623024</v>
+        <v>1444.800723714074</v>
       </c>
       <c r="E9">
-        <v>-331.338</v>
+        <v>-316.2719999999999</v>
       </c>
       <c r="F9">
-        <v>105.462</v>
+        <v>120.528</v>
       </c>
       <c r="G9">
         <v>23.8</v>
@@ -2019,28 +2019,28 @@
         <v>125.25</v>
       </c>
       <c r="M9">
-        <v>5.3047386</v>
+        <v>6.062558399999999</v>
       </c>
       <c r="N9">
-        <v>119.9452614</v>
+        <v>119.1874416</v>
       </c>
       <c r="O9">
-        <v>26.387957508</v>
+        <v>26.221237152</v>
       </c>
       <c r="P9">
-        <v>93.55730389199999</v>
+        <v>92.966204448</v>
       </c>
       <c r="Q9">
-        <v>162.557303892</v>
+        <v>161.966204448</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07408327212756181</v>
+        <v>0.07432681565726156</v>
       </c>
       <c r="T9">
-        <v>0.6531933516757926</v>
+        <v>0.6588179135626228</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.61096548659344</v>
+        <v>20.65959480076926</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07151939040468062</v>
+        <v>0.07139495773072879</v>
       </c>
       <c r="C10">
-        <v>1348.072723714074</v>
+        <v>1336.123366133604</v>
       </c>
       <c r="D10">
-        <v>1444.800723714074</v>
+        <v>1447.917366133604</v>
       </c>
       <c r="E10">
-        <v>-316.2719999999999</v>
+        <v>-301.206</v>
       </c>
       <c r="F10">
-        <v>120.528</v>
+        <v>135.594</v>
       </c>
       <c r="G10">
         <v>23.8</v>
@@ -2101,28 +2101,28 @@
         <v>125.25</v>
       </c>
       <c r="M10">
-        <v>6.062558399999999</v>
+        <v>6.8203782</v>
       </c>
       <c r="N10">
-        <v>119.1874416</v>
+        <v>118.4296218</v>
       </c>
       <c r="O10">
-        <v>26.221237152</v>
+        <v>26.054516796</v>
       </c>
       <c r="P10">
-        <v>92.966204448</v>
+        <v>92.37510500400001</v>
       </c>
       <c r="Q10">
-        <v>161.966204448</v>
+        <v>161.375105004</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07432681565726156</v>
+        <v>0.07457571179200966</v>
       </c>
       <c r="T10">
-        <v>0.6588179135626228</v>
+        <v>0.6645660921942185</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.65959480076926</v>
+        <v>18.36408426735046</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07139495773072879</v>
+        <v>0.07127052505677693</v>
       </c>
       <c r="C11">
-        <v>1336.123366133604</v>
+        <v>1324.187483710552</v>
       </c>
       <c r="D11">
-        <v>1447.917366133604</v>
+        <v>1451.047483710552</v>
       </c>
       <c r="E11">
-        <v>-301.206</v>
+        <v>-286.14</v>
       </c>
       <c r="F11">
-        <v>135.594</v>
+        <v>150.66</v>
       </c>
       <c r="G11">
         <v>23.8</v>
@@ -2183,28 +2183,28 @@
         <v>125.25</v>
       </c>
       <c r="M11">
-        <v>6.8203782</v>
+        <v>7.578197999999998</v>
       </c>
       <c r="N11">
-        <v>118.4296218</v>
+        <v>117.671802</v>
       </c>
       <c r="O11">
-        <v>26.054516796</v>
+        <v>25.88779644</v>
       </c>
       <c r="P11">
-        <v>92.37510500400001</v>
+        <v>91.78400556</v>
       </c>
       <c r="Q11">
-        <v>161.375105004</v>
+        <v>160.78400556</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07457571179200966</v>
+        <v>0.07483013895197438</v>
       </c>
       <c r="T11">
-        <v>0.6645660921942185</v>
+        <v>0.6704420081287386</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.36408426735046</v>
+        <v>16.52767584061541</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07127052505677693</v>
+        <v>0.07114609238282509</v>
       </c>
       <c r="C12">
-        <v>1324.187483710552</v>
+        <v>1312.265164026313</v>
       </c>
       <c r="D12">
-        <v>1451.047483710552</v>
+        <v>1454.191164026312</v>
       </c>
       <c r="E12">
-        <v>-286.14</v>
+        <v>-271.074</v>
       </c>
       <c r="F12">
-        <v>150.66</v>
+        <v>165.726</v>
       </c>
       <c r="G12">
         <v>23.8</v>
@@ -2265,28 +2265,28 @@
         <v>125.25</v>
       </c>
       <c r="M12">
-        <v>7.578198</v>
+        <v>8.336017799999999</v>
       </c>
       <c r="N12">
-        <v>117.671802</v>
+        <v>116.9139822</v>
       </c>
       <c r="O12">
-        <v>25.88779644</v>
+        <v>25.721076084</v>
       </c>
       <c r="P12">
-        <v>91.78400556</v>
+        <v>91.192906116</v>
       </c>
       <c r="Q12">
-        <v>160.78400556</v>
+        <v>160.192906116</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07483013895197438</v>
+        <v>0.07509028357620796</v>
       </c>
       <c r="T12">
-        <v>0.6704420081287386</v>
+        <v>0.676449967117967</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.52767584061541</v>
+        <v>15.02515985510492</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07114609238282509</v>
+        <v>0.07102165970887324</v>
       </c>
       <c r="C13">
-        <v>1312.265164026313</v>
+        <v>1300.356495422903</v>
       </c>
       <c r="D13">
-        <v>1454.191164026312</v>
+        <v>1457.348495422903</v>
       </c>
       <c r="E13">
-        <v>-271.074</v>
+        <v>-256.008</v>
       </c>
       <c r="F13">
-        <v>165.726</v>
+        <v>180.792</v>
       </c>
       <c r="G13">
         <v>23.8</v>
@@ -2347,28 +2347,28 @@
         <v>125.25</v>
       </c>
       <c r="M13">
-        <v>8.336017799999999</v>
+        <v>9.093837599999999</v>
       </c>
       <c r="N13">
-        <v>116.9139822</v>
+        <v>116.1561624</v>
       </c>
       <c r="O13">
-        <v>25.721076084</v>
+        <v>25.554355728</v>
       </c>
       <c r="P13">
-        <v>91.192906116</v>
+        <v>90.601806672</v>
       </c>
       <c r="Q13">
-        <v>160.192906116</v>
+        <v>159.601806672</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07509028357620796</v>
+        <v>0.07535634057826504</v>
       </c>
       <c r="T13">
-        <v>0.676449967117967</v>
+        <v>0.6825944706296778</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.02515985510492</v>
+        <v>13.77306320051284</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07102165970887324</v>
+        <v>0.07104932703492138</v>
       </c>
       <c r="C14">
-        <v>1300.356495422903</v>
+        <v>1284.587285114408</v>
       </c>
       <c r="D14">
-        <v>1457.348495422903</v>
+        <v>1456.645285114408</v>
       </c>
       <c r="E14">
-        <v>-256.008</v>
+        <v>-240.942</v>
       </c>
       <c r="F14">
-        <v>180.792</v>
+        <v>195.858</v>
       </c>
       <c r="G14">
         <v>23.8</v>
@@ -2429,45 +2429,45 @@
         <v>125.25</v>
       </c>
       <c r="M14">
-        <v>9.093837599999999</v>
+        <v>10.1454444</v>
       </c>
       <c r="N14">
-        <v>116.1561624</v>
+        <v>115.1045556</v>
       </c>
       <c r="O14">
-        <v>25.554355728</v>
+        <v>25.323002232</v>
       </c>
       <c r="P14">
-        <v>90.601806672</v>
+        <v>89.781553368</v>
       </c>
       <c r="Q14">
-        <v>159.601806672</v>
+        <v>158.781553368</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07535634057826504</v>
+        <v>0.07562851383324297</v>
       </c>
       <c r="T14">
-        <v>0.6825944706296778</v>
+        <v>0.6888802270956808</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.77306320051284</v>
+        <v>12.34544245296933</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07104932703492138</v>
+        <v>0.07093659436096954</v>
       </c>
       <c r="C15">
-        <v>1284.587285114408</v>
+        <v>1272.390829480909</v>
       </c>
       <c r="D15">
-        <v>1456.645285114408</v>
+        <v>1459.514829480909</v>
       </c>
       <c r="E15">
-        <v>-240.942</v>
+        <v>-225.8759999999999</v>
       </c>
       <c r="F15">
-        <v>195.858</v>
+        <v>210.924</v>
       </c>
       <c r="G15">
         <v>23.8</v>
@@ -2511,28 +2511,28 @@
         <v>125.25</v>
       </c>
       <c r="M15">
-        <v>10.1454444</v>
+        <v>10.9258632</v>
       </c>
       <c r="N15">
-        <v>115.1045556</v>
+        <v>114.3241368</v>
       </c>
       <c r="O15">
-        <v>25.323002232</v>
+        <v>25.151310096</v>
       </c>
       <c r="P15">
-        <v>89.781553368</v>
+        <v>89.172826704</v>
       </c>
       <c r="Q15">
-        <v>158.781553368</v>
+        <v>158.172826704</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07562851383324297</v>
+        <v>0.07590701669880179</v>
       </c>
       <c r="T15">
-        <v>0.6888802270956808</v>
+        <v>0.6953121639446141</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.34544245296933</v>
+        <v>11.4636251349001</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07093659436096954</v>
+        <v>0.07082386168701768</v>
       </c>
       <c r="C16">
-        <v>1272.390829480909</v>
+        <v>1260.205701983712</v>
       </c>
       <c r="D16">
-        <v>1459.514829480909</v>
+        <v>1462.395701983712</v>
       </c>
       <c r="E16">
-        <v>-225.8759999999999</v>
+        <v>-210.8099999999999</v>
       </c>
       <c r="F16">
-        <v>210.924</v>
+        <v>225.99</v>
       </c>
       <c r="G16">
         <v>23.8</v>
@@ -2593,28 +2593,28 @@
         <v>125.25</v>
       </c>
       <c r="M16">
-        <v>10.9258632</v>
+        <v>11.706282</v>
       </c>
       <c r="N16">
-        <v>114.3241368</v>
+        <v>113.543718</v>
       </c>
       <c r="O16">
-        <v>25.151310096</v>
+        <v>24.97961796</v>
       </c>
       <c r="P16">
-        <v>89.172826704</v>
+        <v>88.56410004</v>
       </c>
       <c r="Q16">
-        <v>158.172826704</v>
+        <v>157.56410004</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07590701669880179</v>
+        <v>0.07619207257296198</v>
       </c>
       <c r="T16">
-        <v>0.6953121639446141</v>
+        <v>0.7018954404841107</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.4636251349001</v>
+        <v>10.69938345924009</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07082386168701768</v>
+        <v>0.07071112901306584</v>
       </c>
       <c r="C17">
-        <v>1260.205701983712</v>
+        <v>1248.031969835823</v>
       </c>
       <c r="D17">
-        <v>1462.395701983712</v>
+        <v>1465.287969835823</v>
       </c>
       <c r="E17">
-        <v>-210.81</v>
+        <v>-195.744</v>
       </c>
       <c r="F17">
-        <v>225.99</v>
+        <v>241.056</v>
       </c>
       <c r="G17">
         <v>23.8</v>
@@ -2675,28 +2675,28 @@
         <v>125.25</v>
       </c>
       <c r="M17">
-        <v>11.706282</v>
+        <v>12.4867008</v>
       </c>
       <c r="N17">
-        <v>113.543718</v>
+        <v>112.7632992</v>
       </c>
       <c r="O17">
-        <v>24.97961796</v>
+        <v>24.807925824</v>
       </c>
       <c r="P17">
-        <v>88.56410004</v>
+        <v>87.95537337600001</v>
       </c>
       <c r="Q17">
-        <v>157.56410004</v>
+        <v>156.955373376</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07619207257296198</v>
+        <v>0.07648391549174505</v>
       </c>
       <c r="T17">
-        <v>0.7018954404841107</v>
+        <v>0.708635461703119</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.69938345924009</v>
+        <v>10.03067199303758</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07071112901306584</v>
+        <v>0.07082381633911398</v>
       </c>
       <c r="C18">
-        <v>1248.031969835823</v>
+        <v>1230.074863133322</v>
       </c>
       <c r="D18">
-        <v>1465.287969835823</v>
+        <v>1462.396863133322</v>
       </c>
       <c r="E18">
-        <v>-195.744</v>
+        <v>-180.6779999999999</v>
       </c>
       <c r="F18">
-        <v>241.056</v>
+        <v>256.122</v>
       </c>
       <c r="G18">
         <v>23.8</v>
@@ -2757,45 +2757,45 @@
         <v>125.25</v>
       </c>
       <c r="M18">
-        <v>12.4867008</v>
+        <v>13.702527</v>
       </c>
       <c r="N18">
-        <v>112.7632992</v>
+        <v>111.547473</v>
       </c>
       <c r="O18">
-        <v>24.807925824</v>
+        <v>24.54044406</v>
       </c>
       <c r="P18">
-        <v>87.95537337600001</v>
+        <v>87.00702894</v>
       </c>
       <c r="Q18">
-        <v>156.955373376</v>
+        <v>156.00702894</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07648391549174505</v>
+        <v>0.07678279077001685</v>
       </c>
       <c r="T18">
-        <v>0.708635461703119</v>
+        <v>0.7155378930719829</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.03067199303758</v>
+        <v>9.140649750224904</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07082381633911398</v>
+        <v>0.07072434366516214</v>
       </c>
       <c r="C19">
-        <v>1230.074863133322</v>
+        <v>1217.560343120521</v>
       </c>
       <c r="D19">
-        <v>1462.396863133322</v>
+        <v>1464.948343120521</v>
       </c>
       <c r="E19">
-        <v>-180.6779999999999</v>
+        <v>-165.612</v>
       </c>
       <c r="F19">
-        <v>256.122</v>
+        <v>271.188</v>
       </c>
       <c r="G19">
         <v>23.8</v>
@@ -2839,28 +2839,28 @@
         <v>125.25</v>
       </c>
       <c r="M19">
-        <v>13.702527</v>
+        <v>14.508558</v>
       </c>
       <c r="N19">
-        <v>111.547473</v>
+        <v>110.741442</v>
       </c>
       <c r="O19">
-        <v>24.54044406</v>
+        <v>24.36311724</v>
       </c>
       <c r="P19">
-        <v>87.00702894</v>
+        <v>86.37832476</v>
       </c>
       <c r="Q19">
-        <v>156.00702894</v>
+        <v>155.37832476</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07678279077001685</v>
+        <v>0.07708895568922212</v>
       </c>
       <c r="T19">
-        <v>0.7155378930719829</v>
+        <v>0.7226086764254533</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.140649750224904</v>
+        <v>8.632835875212411</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07072434366516214</v>
+        <v>0.07062487099121029</v>
       </c>
       <c r="C20">
-        <v>1217.560343120521</v>
+        <v>1205.054741929126</v>
       </c>
       <c r="D20">
-        <v>1464.948343120521</v>
+        <v>1467.508741929126</v>
       </c>
       <c r="E20">
-        <v>-165.612</v>
+        <v>-150.546</v>
       </c>
       <c r="F20">
-        <v>271.188</v>
+        <v>286.254</v>
       </c>
       <c r="G20">
         <v>23.8</v>
@@ -2921,28 +2921,28 @@
         <v>125.25</v>
       </c>
       <c r="M20">
-        <v>14.508558</v>
+        <v>15.314589</v>
       </c>
       <c r="N20">
-        <v>110.741442</v>
+        <v>109.935411</v>
       </c>
       <c r="O20">
-        <v>24.36311724</v>
+        <v>24.18579042</v>
       </c>
       <c r="P20">
-        <v>86.37832476</v>
+        <v>85.74962058</v>
       </c>
       <c r="Q20">
-        <v>155.37832476</v>
+        <v>154.74962058</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07708895568922211</v>
+        <v>0.07740268023606209</v>
       </c>
       <c r="T20">
-        <v>0.7226086764254531</v>
+        <v>0.7298540470222191</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.632835875212411</v>
+        <v>8.178476092306493</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07062487099121029</v>
+        <v>0.07052539831725844</v>
       </c>
       <c r="C21">
-        <v>1205.054741929126</v>
+        <v>1192.558106405266</v>
       </c>
       <c r="D21">
-        <v>1467.508741929126</v>
+        <v>1470.078106405266</v>
       </c>
       <c r="E21">
-        <v>-150.546</v>
+        <v>-135.48</v>
       </c>
       <c r="F21">
-        <v>286.254</v>
+        <v>301.32</v>
       </c>
       <c r="G21">
         <v>23.8</v>
@@ -3003,28 +3003,28 @@
         <v>125.25</v>
       </c>
       <c r="M21">
-        <v>15.314589</v>
+        <v>16.12062</v>
       </c>
       <c r="N21">
-        <v>109.935411</v>
+        <v>109.12938</v>
       </c>
       <c r="O21">
-        <v>24.18579042</v>
+        <v>24.0084636</v>
       </c>
       <c r="P21">
-        <v>85.74962058</v>
+        <v>85.1209164</v>
       </c>
       <c r="Q21">
-        <v>154.74962058</v>
+        <v>154.1209164</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07740268023606209</v>
+        <v>0.07772424789657305</v>
       </c>
       <c r="T21">
-        <v>0.7298540470222191</v>
+        <v>0.7372805518839043</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.178476092306493</v>
+        <v>7.769552287691169</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07052539831725844</v>
+        <v>0.07055696564330659</v>
       </c>
       <c r="C22">
-        <v>1192.558106405266</v>
+        <v>1176.675753025303</v>
       </c>
       <c r="D22">
-        <v>1470.078106405266</v>
+        <v>1469.261753025304</v>
       </c>
       <c r="E22">
-        <v>-135.48</v>
+        <v>-120.4139999999999</v>
       </c>
       <c r="F22">
-        <v>301.32</v>
+        <v>316.386</v>
       </c>
       <c r="G22">
         <v>23.8</v>
@@ -3085,45 +3085,45 @@
         <v>125.25</v>
       </c>
       <c r="M22">
-        <v>16.12062</v>
+        <v>17.1797598</v>
       </c>
       <c r="N22">
-        <v>109.12938</v>
+        <v>108.0702402</v>
       </c>
       <c r="O22">
-        <v>24.0084636</v>
+        <v>23.775452844</v>
       </c>
       <c r="P22">
-        <v>85.1209164</v>
+        <v>84.294787356</v>
       </c>
       <c r="Q22">
-        <v>154.1209164</v>
+        <v>153.294787356</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07772424789657305</v>
+        <v>0.07805395651051467</v>
       </c>
       <c r="T22">
-        <v>0.7372805518839043</v>
+        <v>0.7448950695268979</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.769552287691169</v>
+        <v>7.290555948285143</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07055696564330659</v>
+        <v>0.07046373296935474</v>
       </c>
       <c r="C23">
-        <v>1176.675753025303</v>
+        <v>1164.023435685983</v>
       </c>
       <c r="D23">
-        <v>1469.261753025304</v>
+        <v>1471.675435685984</v>
       </c>
       <c r="E23">
-        <v>-120.414</v>
+        <v>-105.348</v>
       </c>
       <c r="F23">
-        <v>316.386</v>
+        <v>331.452</v>
       </c>
       <c r="G23">
         <v>23.8</v>
@@ -3167,28 +3167,28 @@
         <v>125.25</v>
       </c>
       <c r="M23">
-        <v>17.1797598</v>
+        <v>17.9978436</v>
       </c>
       <c r="N23">
-        <v>108.0702402</v>
+        <v>107.2521564</v>
       </c>
       <c r="O23">
-        <v>23.775452844</v>
+        <v>23.595474408</v>
       </c>
       <c r="P23">
-        <v>84.294787356</v>
+        <v>83.656681992</v>
       </c>
       <c r="Q23">
-        <v>153.294787356</v>
+        <v>152.656681992</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07805395651051467</v>
+        <v>0.07839211919148042</v>
       </c>
       <c r="T23">
-        <v>0.7448950695268977</v>
+        <v>0.7527048312120194</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.290555948285144</v>
+        <v>6.959167041544911</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07046373296935474</v>
+        <v>0.0703705002954029</v>
       </c>
       <c r="C24">
-        <v>1164.023435685983</v>
+        <v>1151.379061724173</v>
       </c>
       <c r="D24">
-        <v>1471.675435685984</v>
+        <v>1474.097061724173</v>
       </c>
       <c r="E24">
-        <v>-105.348</v>
+        <v>-90.28199999999998</v>
       </c>
       <c r="F24">
-        <v>331.452</v>
+        <v>346.518</v>
       </c>
       <c r="G24">
         <v>23.8</v>
@@ -3249,28 +3249,28 @@
         <v>125.25</v>
       </c>
       <c r="M24">
-        <v>17.9978436</v>
+        <v>18.8159274</v>
       </c>
       <c r="N24">
-        <v>107.2521564</v>
+        <v>106.4340726</v>
       </c>
       <c r="O24">
-        <v>23.595474408</v>
+        <v>23.415495972</v>
       </c>
       <c r="P24">
-        <v>83.656681992</v>
+        <v>83.01857662800001</v>
       </c>
       <c r="Q24">
-        <v>152.656681992</v>
+        <v>152.018576628</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07839211919148042</v>
+        <v>0.07873906531870506</v>
       </c>
       <c r="T24">
-        <v>0.7527048312120194</v>
+        <v>0.7607174438500013</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.959167041544911</v>
+        <v>6.656594561477741</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0703705002954029</v>
+        <v>0.07027726762145103</v>
       </c>
       <c r="C25">
-        <v>1151.379061724173</v>
+        <v>1138.742670416729</v>
       </c>
       <c r="D25">
-        <v>1474.097061724173</v>
+        <v>1476.52667041673</v>
       </c>
       <c r="E25">
-        <v>-90.28199999999998</v>
+        <v>-75.21599999999995</v>
       </c>
       <c r="F25">
-        <v>346.518</v>
+        <v>361.584</v>
       </c>
       <c r="G25">
         <v>23.8</v>
@@ -3331,28 +3331,28 @@
         <v>125.25</v>
       </c>
       <c r="M25">
-        <v>18.8159274</v>
+        <v>19.6340112</v>
       </c>
       <c r="N25">
-        <v>106.4340726</v>
+        <v>105.6159888</v>
       </c>
       <c r="O25">
-        <v>23.415495972</v>
+        <v>23.235517536</v>
       </c>
       <c r="P25">
-        <v>83.01857662800001</v>
+        <v>82.38047126399999</v>
       </c>
       <c r="Q25">
-        <v>152.018576628</v>
+        <v>151.380471264</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07873906531870506</v>
+        <v>0.07909514160717242</v>
       </c>
       <c r="T25">
-        <v>0.7607174438500013</v>
+        <v>0.7689409147152985</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.656594561477741</v>
+        <v>6.379236454749501</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07027726762145103</v>
+        <v>0.07018403494749918</v>
       </c>
       <c r="C26">
-        <v>1138.74267041673</v>
+        <v>1126.114301299878</v>
       </c>
       <c r="D26">
-        <v>1476.52667041673</v>
+        <v>1478.964301299878</v>
       </c>
       <c r="E26">
-        <v>-75.21600000000001</v>
+        <v>-60.14999999999998</v>
       </c>
       <c r="F26">
-        <v>361.5839999999999</v>
+        <v>376.65</v>
       </c>
       <c r="G26">
         <v>23.8</v>
@@ -3413,28 +3413,28 @@
         <v>125.25</v>
       </c>
       <c r="M26">
-        <v>19.6340112</v>
+        <v>20.452095</v>
       </c>
       <c r="N26">
-        <v>105.6159888</v>
+        <v>104.797905</v>
       </c>
       <c r="O26">
-        <v>23.235517536</v>
+        <v>23.0555391</v>
       </c>
       <c r="P26">
-        <v>82.38047126399999</v>
+        <v>81.7423659</v>
       </c>
       <c r="Q26">
-        <v>151.380471264</v>
+        <v>150.7423659</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07909514160717242</v>
+        <v>0.07946071326333225</v>
       </c>
       <c r="T26">
-        <v>0.7689409147152985</v>
+        <v>0.7773836781370036</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.379236454749502</v>
+        <v>6.124066996559521</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07018403494749918</v>
+        <v>0.07029360227354735</v>
       </c>
       <c r="C27">
-        <v>1126.114301299878</v>
+        <v>1108.184416969726</v>
       </c>
       <c r="D27">
-        <v>1478.964301299878</v>
+        <v>1476.100416969726</v>
       </c>
       <c r="E27">
-        <v>-60.14999999999998</v>
+        <v>-45.08399999999995</v>
       </c>
       <c r="F27">
-        <v>376.65</v>
+        <v>391.716</v>
       </c>
       <c r="G27">
         <v>23.8</v>
@@ -3495,45 +3495,45 @@
         <v>125.25</v>
       </c>
       <c r="M27">
-        <v>20.452095</v>
+        <v>21.6618948</v>
       </c>
       <c r="N27">
-        <v>104.797905</v>
+        <v>103.5881052</v>
       </c>
       <c r="O27">
-        <v>23.0555391</v>
+        <v>22.789383144</v>
       </c>
       <c r="P27">
-        <v>81.7423659</v>
+        <v>80.798722056</v>
       </c>
       <c r="Q27">
-        <v>150.7423659</v>
+        <v>149.798722056</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07946071326333225</v>
+        <v>0.07983616523452344</v>
       </c>
       <c r="T27">
-        <v>0.7773836781370036</v>
+        <v>0.7860546243538901</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.124066996559521</v>
+        <v>5.782042667846397</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07029360227354735</v>
+        <v>0.07020816959959549</v>
       </c>
       <c r="C28">
-        <v>1108.184416969726</v>
+        <v>1095.3505128551</v>
       </c>
       <c r="D28">
-        <v>1476.100416969726</v>
+        <v>1478.3325128551</v>
       </c>
       <c r="E28">
-        <v>-45.08399999999995</v>
+        <v>-30.01799999999997</v>
       </c>
       <c r="F28">
-        <v>391.716</v>
+        <v>406.782</v>
       </c>
       <c r="G28">
         <v>23.8</v>
@@ -3577,28 +3577,28 @@
         <v>125.25</v>
       </c>
       <c r="M28">
-        <v>21.6618948</v>
+        <v>22.4950446</v>
       </c>
       <c r="N28">
-        <v>103.5881052</v>
+        <v>102.7549554</v>
       </c>
       <c r="O28">
-        <v>22.789383144</v>
+        <v>22.606090188</v>
       </c>
       <c r="P28">
-        <v>80.798722056</v>
+        <v>80.148865212</v>
       </c>
       <c r="Q28">
-        <v>149.798722056</v>
+        <v>149.148865212</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07983616523452344</v>
+        <v>0.08022190356108971</v>
       </c>
       <c r="T28">
-        <v>0.7860546243538901</v>
+        <v>0.794963130741102</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.782042667846397</v>
+        <v>5.567892939407642</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07020816959959549</v>
+        <v>0.07012273692564364</v>
       </c>
       <c r="C29">
-        <v>1095.3505128551</v>
+        <v>1082.523369523605</v>
       </c>
       <c r="D29">
-        <v>1478.3325128551</v>
+        <v>1480.571369523605</v>
       </c>
       <c r="E29">
-        <v>-30.01799999999997</v>
+        <v>-14.95199999999994</v>
       </c>
       <c r="F29">
-        <v>406.782</v>
+        <v>421.848</v>
       </c>
       <c r="G29">
         <v>23.8</v>
@@ -3659,28 +3659,28 @@
         <v>125.25</v>
       </c>
       <c r="M29">
-        <v>22.4950446</v>
+        <v>23.3281944</v>
       </c>
       <c r="N29">
-        <v>102.7549554</v>
+        <v>101.9218056</v>
       </c>
       <c r="O29">
-        <v>22.606090188</v>
+        <v>22.422797232</v>
       </c>
       <c r="P29">
-        <v>80.148865212</v>
+        <v>79.49900836800001</v>
       </c>
       <c r="Q29">
-        <v>149.148865212</v>
+        <v>148.499008368</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08022190356108971</v>
+        <v>0.08061835684117172</v>
       </c>
       <c r="T29">
-        <v>0.794963130741102</v>
+        <v>0.8041190956390699</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.567892939407642</v>
+        <v>5.369039620143083</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07012273692564364</v>
+        <v>0.07003730425169179</v>
       </c>
       <c r="C30">
-        <v>1082.523369523605</v>
+        <v>1069.703017738379</v>
       </c>
       <c r="D30">
-        <v>1480.571369523605</v>
+        <v>1482.817017738379</v>
       </c>
       <c r="E30">
-        <v>-14.95199999999994</v>
+        <v>0.1140000000000896</v>
       </c>
       <c r="F30">
-        <v>421.848</v>
+        <v>436.914</v>
       </c>
       <c r="G30">
         <v>23.8</v>
@@ -3741,28 +3741,28 @@
         <v>125.25</v>
       </c>
       <c r="M30">
-        <v>23.3281944</v>
+        <v>24.1613442</v>
       </c>
       <c r="N30">
-        <v>101.9218056</v>
+        <v>101.0886558</v>
       </c>
       <c r="O30">
-        <v>22.422797232</v>
+        <v>22.239504276</v>
       </c>
       <c r="P30">
-        <v>79.49900836800001</v>
+        <v>78.84915152400001</v>
       </c>
       <c r="Q30">
-        <v>148.499008368</v>
+        <v>147.849151524</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08061835684117172</v>
+        <v>0.08102597781928421</v>
       </c>
       <c r="T30">
-        <v>0.8041190956390699</v>
+        <v>0.8135329750412059</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.369039620143083</v>
+        <v>5.183900322896769</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07003730425169179</v>
+        <v>0.06995187157773994</v>
       </c>
       <c r="C31">
-        <v>1069.703017738379</v>
+        <v>1056.889488449484</v>
       </c>
       <c r="D31">
-        <v>1482.817017738379</v>
+        <v>1485.069488449484</v>
       </c>
       <c r="E31">
-        <v>0.1139999999999759</v>
+        <v>15.18000000000001</v>
       </c>
       <c r="F31">
-        <v>436.9139999999999</v>
+        <v>451.98</v>
       </c>
       <c r="G31">
         <v>23.8</v>
@@ -3823,28 +3823,28 @@
         <v>125.25</v>
       </c>
       <c r="M31">
-        <v>24.1613442</v>
+        <v>24.994494</v>
       </c>
       <c r="N31">
-        <v>101.0886558</v>
+        <v>100.255506</v>
       </c>
       <c r="O31">
-        <v>22.239504276</v>
+        <v>22.05621132</v>
       </c>
       <c r="P31">
-        <v>78.84915152400001</v>
+        <v>78.19929467999999</v>
       </c>
       <c r="Q31">
-        <v>147.849151524</v>
+        <v>147.19929468</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08102597781928421</v>
+        <v>0.08144524511105705</v>
       </c>
       <c r="T31">
-        <v>0.8135329750412059</v>
+        <v>0.82321582242626</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.18390032289677</v>
+        <v>5.011103645466878</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06995187157773994</v>
+        <v>0.06986643890378809</v>
       </c>
       <c r="C32">
-        <v>1056.889488449484</v>
+        <v>1044.082812795325</v>
       </c>
       <c r="D32">
-        <v>1485.069488449484</v>
+        <v>1487.328812795325</v>
       </c>
       <c r="E32">
-        <v>15.18000000000001</v>
+        <v>30.24600000000004</v>
       </c>
       <c r="F32">
-        <v>451.98</v>
+        <v>467.046</v>
       </c>
       <c r="G32">
         <v>23.8</v>
@@ -3905,28 +3905,28 @@
         <v>125.25</v>
       </c>
       <c r="M32">
-        <v>24.994494</v>
+        <v>25.8276438</v>
       </c>
       <c r="N32">
-        <v>100.255506</v>
+        <v>99.4223562</v>
       </c>
       <c r="O32">
-        <v>22.05621132</v>
+        <v>21.872918364</v>
       </c>
       <c r="P32">
-        <v>78.19929467999999</v>
+        <v>77.549437836</v>
       </c>
       <c r="Q32">
-        <v>147.19929468</v>
+        <v>146.549437836</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08144524511105705</v>
+        <v>0.08187666507795376</v>
       </c>
       <c r="T32">
-        <v>0.82321582242626</v>
+        <v>0.8331793320543593</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.011103645466878</v>
+        <v>4.849455140774397</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06986643890378809</v>
+        <v>0.06978100622983624</v>
       </c>
       <c r="C33">
-        <v>1044.082812795325</v>
+        <v>1031.283022104088</v>
       </c>
       <c r="D33">
-        <v>1487.328812795325</v>
+        <v>1489.595022104088</v>
       </c>
       <c r="E33">
-        <v>30.24600000000004</v>
+        <v>45.31200000000001</v>
       </c>
       <c r="F33">
-        <v>467.046</v>
+        <v>482.112</v>
       </c>
       <c r="G33">
         <v>23.8</v>
@@ -3987,28 +3987,28 @@
         <v>125.25</v>
       </c>
       <c r="M33">
-        <v>25.8276438</v>
+        <v>26.6607936</v>
       </c>
       <c r="N33">
-        <v>99.4223562</v>
+        <v>98.58920639999999</v>
       </c>
       <c r="O33">
-        <v>21.872918364</v>
+        <v>21.689625408</v>
       </c>
       <c r="P33">
-        <v>77.549437836</v>
+        <v>76.899580992</v>
       </c>
       <c r="Q33">
-        <v>146.549437836</v>
+        <v>145.899580992</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08187666507795376</v>
+        <v>0.08232077386740624</v>
       </c>
       <c r="T33">
-        <v>0.8331793320543593</v>
+        <v>0.843435886083285</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.849455140774397</v>
+        <v>4.697909667625198</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06978100622983624</v>
+        <v>0.06969557355588439</v>
       </c>
       <c r="C34">
-        <v>1031.283022104088</v>
+        <v>1018.490147895185</v>
       </c>
       <c r="D34">
-        <v>1489.595022104088</v>
+        <v>1491.868147895185</v>
       </c>
       <c r="E34">
-        <v>45.31200000000001</v>
+        <v>60.37800000000004</v>
       </c>
       <c r="F34">
-        <v>482.112</v>
+        <v>497.178</v>
       </c>
       <c r="G34">
         <v>23.8</v>
@@ -4069,28 +4069,28 @@
         <v>125.25</v>
       </c>
       <c r="M34">
-        <v>26.6607936</v>
+        <v>27.4939434</v>
       </c>
       <c r="N34">
-        <v>98.58920639999999</v>
+        <v>97.75605659999999</v>
       </c>
       <c r="O34">
-        <v>21.689625408</v>
+        <v>21.506332452</v>
       </c>
       <c r="P34">
-        <v>76.899580992</v>
+        <v>76.249724148</v>
       </c>
       <c r="Q34">
-        <v>145.899580992</v>
+        <v>145.249724148</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08232077386740624</v>
+        <v>0.08277813963564834</v>
       </c>
       <c r="T34">
-        <v>0.843435886083285</v>
+        <v>0.8539986059041189</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.697909667625198</v>
+        <v>4.555548768606252</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06969557355588439</v>
+        <v>0.07027314088193254</v>
       </c>
       <c r="C35">
-        <v>1018.490147895185</v>
+        <v>988.1903968174207</v>
       </c>
       <c r="D35">
-        <v>1491.868147895185</v>
+        <v>1476.634396817421</v>
       </c>
       <c r="E35">
-        <v>60.37800000000004</v>
+        <v>75.44400000000007</v>
       </c>
       <c r="F35">
-        <v>497.178</v>
+        <v>512.244</v>
       </c>
       <c r="G35">
         <v>23.8</v>
@@ -4151,45 +4151,45 @@
         <v>125.25</v>
       </c>
       <c r="M35">
-        <v>27.4939434</v>
+        <v>29.6077032</v>
       </c>
       <c r="N35">
-        <v>97.75605659999999</v>
+        <v>95.6422968</v>
       </c>
       <c r="O35">
-        <v>21.506332452</v>
+        <v>21.041305296</v>
       </c>
       <c r="P35">
-        <v>76.249724148</v>
+        <v>74.60099150399999</v>
       </c>
       <c r="Q35">
-        <v>145.249724148</v>
+        <v>143.600991504</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08277813963564834</v>
+        <v>0.08324936497262506</v>
       </c>
       <c r="T35">
-        <v>0.8539986059041189</v>
+        <v>0.8648814081437659</v>
       </c>
       <c r="U35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.22</v>
       </c>
       <c r="W35">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.555548768606252</v>
+        <v>4.230318007240764</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07027314088193254</v>
+        <v>0.07020720820798068</v>
       </c>
       <c r="C36">
-        <v>988.1903968174207</v>
+        <v>974.8476695042615</v>
       </c>
       <c r="D36">
-        <v>1476.634396817421</v>
+        <v>1478.357669504262</v>
       </c>
       <c r="E36">
-        <v>75.44400000000007</v>
+        <v>90.5100000000001</v>
       </c>
       <c r="F36">
-        <v>512.244</v>
+        <v>527.3100000000001</v>
       </c>
       <c r="G36">
         <v>23.8</v>
@@ -4233,28 +4233,28 @@
         <v>125.25</v>
       </c>
       <c r="M36">
-        <v>29.6077032</v>
+        <v>30.478518</v>
       </c>
       <c r="N36">
-        <v>95.6422968</v>
+        <v>94.77148199999999</v>
       </c>
       <c r="O36">
-        <v>21.041305296</v>
+        <v>20.84972604</v>
       </c>
       <c r="P36">
-        <v>74.60099150399999</v>
+        <v>73.92175596</v>
       </c>
       <c r="Q36">
-        <v>143.600991504</v>
+        <v>142.92175596</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08324936497262506</v>
+        <v>0.08373508955073952</v>
       </c>
       <c r="T36">
-        <v>0.8648814081437659</v>
+        <v>0.8760990658369406</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.230318007240764</v>
+        <v>4.109451778462455</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07020720820798068</v>
+        <v>0.07112407553402883</v>
       </c>
       <c r="C37">
-        <v>974.8476695042615</v>
+        <v>936.1728188852055</v>
       </c>
       <c r="D37">
-        <v>1478.357669504262</v>
+        <v>1454.748818885206</v>
       </c>
       <c r="E37">
-        <v>90.5100000000001</v>
+        <v>105.576</v>
       </c>
       <c r="F37">
-        <v>527.3100000000001</v>
+        <v>542.376</v>
       </c>
       <c r="G37">
         <v>23.8</v>
@@ -4315,45 +4315,45 @@
         <v>125.25</v>
       </c>
       <c r="M37">
-        <v>30.478518</v>
+        <v>33.2476488</v>
       </c>
       <c r="N37">
-        <v>94.77148199999999</v>
+        <v>92.00235119999999</v>
       </c>
       <c r="O37">
-        <v>20.84972604</v>
+        <v>20.240517264</v>
       </c>
       <c r="P37">
-        <v>73.92175596</v>
+        <v>71.76183393599999</v>
       </c>
       <c r="Q37">
-        <v>142.92175596</v>
+        <v>140.761833936</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08373508955073952</v>
+        <v>0.08423599302192006</v>
       </c>
       <c r="T37">
-        <v>0.8760990658369406</v>
+        <v>0.887667275333027</v>
       </c>
       <c r="U37">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V37">
         <v>0.22</v>
       </c>
       <c r="W37">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.109451778462455</v>
+        <v>3.76718368127132</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07112407553402883</v>
+        <v>0.07108544286007698</v>
       </c>
       <c r="C38">
-        <v>936.1728188852055</v>
+        <v>922.0863628694408</v>
       </c>
       <c r="D38">
-        <v>1454.748818885206</v>
+        <v>1455.728362869441</v>
       </c>
       <c r="E38">
-        <v>105.576</v>
+        <v>120.6420000000001</v>
       </c>
       <c r="F38">
-        <v>542.376</v>
+        <v>557.442</v>
       </c>
       <c r="G38">
         <v>23.8</v>
@@ -4397,28 +4397,28 @@
         <v>125.25</v>
       </c>
       <c r="M38">
-        <v>33.2476488</v>
+        <v>34.1711946</v>
       </c>
       <c r="N38">
-        <v>92.00235119999999</v>
+        <v>91.07880539999999</v>
       </c>
       <c r="O38">
-        <v>20.240517264</v>
+        <v>20.037337188</v>
       </c>
       <c r="P38">
-        <v>71.76183393599999</v>
+        <v>71.041468212</v>
       </c>
       <c r="Q38">
-        <v>140.761833936</v>
+        <v>140.041468212</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08423599302192006</v>
+        <v>0.08475279819059839</v>
       </c>
       <c r="T38">
-        <v>0.8876672753330269</v>
+        <v>0.8996027295750209</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.76718368127132</v>
+        <v>3.665367906101825</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07108544286007698</v>
+        <v>0.07104681018612513</v>
       </c>
       <c r="C39">
-        <v>922.0863628694408</v>
+        <v>908.0012268793961</v>
       </c>
       <c r="D39">
-        <v>1455.728362869441</v>
+        <v>1456.709226879396</v>
       </c>
       <c r="E39">
-        <v>120.6420000000001</v>
+        <v>135.708</v>
       </c>
       <c r="F39">
-        <v>557.442</v>
+        <v>572.5079999999999</v>
       </c>
       <c r="G39">
         <v>23.8</v>
@@ -4479,28 +4479,28 @@
         <v>125.25</v>
       </c>
       <c r="M39">
-        <v>34.1711946</v>
+        <v>35.09474039999999</v>
       </c>
       <c r="N39">
-        <v>91.07880539999999</v>
+        <v>90.15525960000001</v>
       </c>
       <c r="O39">
-        <v>20.037337188</v>
+        <v>19.834157112</v>
       </c>
       <c r="P39">
-        <v>71.041468212</v>
+        <v>70.32110248800001</v>
       </c>
       <c r="Q39">
-        <v>140.041468212</v>
+        <v>139.321102488</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08475279819059839</v>
+        <v>0.08528627449375022</v>
       </c>
       <c r="T39">
-        <v>0.8996027295750209</v>
+        <v>0.9119231984699822</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.665367906101825</v>
+        <v>3.568910855941252</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07104681018612513</v>
+        <v>0.07185993751217329</v>
       </c>
       <c r="C40">
-        <v>908.0012268793961</v>
+        <v>872.5653084728093</v>
       </c>
       <c r="D40">
-        <v>1456.709226879396</v>
+        <v>1436.339308472809</v>
       </c>
       <c r="E40">
-        <v>135.708</v>
+        <v>150.774</v>
       </c>
       <c r="F40">
-        <v>572.5079999999999</v>
+        <v>587.574</v>
       </c>
       <c r="G40">
         <v>23.8</v>
@@ -4561,45 +4561,45 @@
         <v>125.25</v>
       </c>
       <c r="M40">
-        <v>35.09474039999999</v>
+        <v>37.6634934</v>
       </c>
       <c r="N40">
-        <v>90.15525960000001</v>
+        <v>87.58650660000001</v>
       </c>
       <c r="O40">
-        <v>19.834157112</v>
+        <v>19.269031452</v>
       </c>
       <c r="P40">
-        <v>70.32110248800001</v>
+        <v>68.317475148</v>
       </c>
       <c r="Q40">
-        <v>139.321102488</v>
+        <v>137.317475148</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08528627449375022</v>
+        <v>0.08583724182323491</v>
       </c>
       <c r="T40">
-        <v>0.9119231984699822</v>
+        <v>0.9246476171647785</v>
       </c>
       <c r="U40">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V40">
         <v>0.22</v>
       </c>
       <c r="W40">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.568910855941252</v>
+        <v>3.325501399187788</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07185993751217329</v>
+        <v>0.07184314483822143</v>
       </c>
       <c r="C41">
-        <v>872.5653084728093</v>
+        <v>857.9142244901601</v>
       </c>
       <c r="D41">
-        <v>1436.339308472809</v>
+        <v>1436.75422449016</v>
       </c>
       <c r="E41">
-        <v>150.774</v>
+        <v>165.84</v>
       </c>
       <c r="F41">
-        <v>587.574</v>
+        <v>602.64</v>
       </c>
       <c r="G41">
         <v>23.8</v>
@@ -4643,28 +4643,28 @@
         <v>125.25</v>
       </c>
       <c r="M41">
-        <v>37.6634934</v>
+        <v>38.629224</v>
       </c>
       <c r="N41">
-        <v>87.58650660000001</v>
+        <v>86.62077600000001</v>
       </c>
       <c r="O41">
-        <v>19.269031452</v>
+        <v>19.05657072</v>
       </c>
       <c r="P41">
-        <v>68.317475148</v>
+        <v>67.56420528000001</v>
       </c>
       <c r="Q41">
-        <v>137.317475148</v>
+        <v>136.56420528</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08583724182323491</v>
+        <v>0.08640657473036906</v>
       </c>
       <c r="T41">
-        <v>0.9246476171647785</v>
+        <v>0.9377961831494012</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.325501399187788</v>
+        <v>3.242363864208093</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07184314483822143</v>
+        <v>0.07182635216426959</v>
       </c>
       <c r="C42">
-        <v>857.9142244901601</v>
+        <v>843.2633802907507</v>
       </c>
       <c r="D42">
-        <v>1436.75422449016</v>
+        <v>1437.169380290751</v>
       </c>
       <c r="E42">
-        <v>165.84</v>
+        <v>180.9060000000001</v>
       </c>
       <c r="F42">
-        <v>602.64</v>
+        <v>617.706</v>
       </c>
       <c r="G42">
         <v>23.8</v>
@@ -4725,28 +4725,28 @@
         <v>125.25</v>
       </c>
       <c r="M42">
-        <v>38.629224</v>
+        <v>39.5949546</v>
       </c>
       <c r="N42">
-        <v>86.62077600000001</v>
+        <v>85.65504540000001</v>
       </c>
       <c r="O42">
-        <v>19.05657072</v>
+        <v>18.844109988</v>
       </c>
       <c r="P42">
-        <v>67.56420528000001</v>
+        <v>66.81093541200001</v>
       </c>
       <c r="Q42">
-        <v>136.56420528</v>
+        <v>135.810935412</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08640657473036906</v>
+        <v>0.08699520705808406</v>
       </c>
       <c r="T42">
-        <v>0.9377961831494012</v>
+        <v>0.9513904632351976</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.242363864208093</v>
+        <v>3.163281818739603</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07182635216426959</v>
+        <v>0.07180955949031774</v>
       </c>
       <c r="C43">
-        <v>843.2633802907507</v>
+        <v>828.6127760825001</v>
       </c>
       <c r="D43">
-        <v>1437.169380290751</v>
+        <v>1437.5847760825</v>
       </c>
       <c r="E43">
-        <v>180.9060000000001</v>
+        <v>195.9720000000001</v>
       </c>
       <c r="F43">
-        <v>617.706</v>
+        <v>632.772</v>
       </c>
       <c r="G43">
         <v>23.8</v>
@@ -4807,28 +4807,28 @@
         <v>125.25</v>
       </c>
       <c r="M43">
-        <v>39.5949546</v>
+        <v>40.56068520000001</v>
       </c>
       <c r="N43">
-        <v>85.65504540000001</v>
+        <v>84.68931479999999</v>
       </c>
       <c r="O43">
-        <v>18.844109988</v>
+        <v>18.631649256</v>
       </c>
       <c r="P43">
-        <v>66.81093541200001</v>
+        <v>66.05766554399999</v>
       </c>
       <c r="Q43">
-        <v>135.810935412</v>
+        <v>135.057665544</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08699520705808406</v>
+        <v>0.08760413705227196</v>
       </c>
       <c r="T43">
-        <v>0.9513904632351976</v>
+        <v>0.9654535115998145</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.163281818739603</v>
+        <v>3.087965584960088</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07180955949031775</v>
+        <v>0.0717927668163659</v>
       </c>
       <c r="C44">
-        <v>828.6127760824997</v>
+        <v>813.9624120735675</v>
       </c>
       <c r="D44">
-        <v>1437.5847760825</v>
+        <v>1438.000412073568</v>
       </c>
       <c r="E44">
-        <v>195.972</v>
+        <v>211.038</v>
       </c>
       <c r="F44">
-        <v>632.7719999999999</v>
+        <v>647.838</v>
       </c>
       <c r="G44">
         <v>23.8</v>
@@ -4889,28 +4889,28 @@
         <v>125.25</v>
       </c>
       <c r="M44">
-        <v>40.5606852</v>
+        <v>41.5264158</v>
       </c>
       <c r="N44">
-        <v>84.68931480000001</v>
+        <v>83.7235842</v>
       </c>
       <c r="O44">
-        <v>18.631649256</v>
+        <v>18.419188524</v>
       </c>
       <c r="P44">
-        <v>66.057665544</v>
+        <v>65.304395676</v>
       </c>
       <c r="Q44">
-        <v>135.057665544</v>
+        <v>134.304395676</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08760413705227196</v>
+        <v>0.08823443301116823</v>
       </c>
       <c r="T44">
-        <v>0.9654535115998145</v>
+        <v>0.9800100002579268</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.087965584960088</v>
+        <v>3.016152431821482</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0717927668163659</v>
+        <v>0.07445293414241405</v>
       </c>
       <c r="C45">
-        <v>813.9624120735675</v>
+        <v>735.9198411306411</v>
       </c>
       <c r="D45">
-        <v>1438.000412073568</v>
+        <v>1375.023841130641</v>
       </c>
       <c r="E45">
-        <v>211.038</v>
+        <v>226.104</v>
       </c>
       <c r="F45">
-        <v>647.838</v>
+        <v>662.904</v>
       </c>
       <c r="G45">
         <v>23.8</v>
@@ -4971,45 +4971,45 @@
         <v>125.25</v>
       </c>
       <c r="M45">
-        <v>41.5264158</v>
+        <v>47.6627976</v>
       </c>
       <c r="N45">
-        <v>83.7235842</v>
+        <v>77.5872024</v>
       </c>
       <c r="O45">
-        <v>18.419188524</v>
+        <v>17.069184528</v>
       </c>
       <c r="P45">
-        <v>65.304395676</v>
+        <v>60.518017872</v>
       </c>
       <c r="Q45">
-        <v>134.304395676</v>
+        <v>129.518017872</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08823443301116823</v>
+        <v>0.08888723954002507</v>
       </c>
       <c r="T45">
-        <v>0.9800100002579268</v>
+        <v>0.9950863635109718</v>
       </c>
       <c r="U45">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V45">
         <v>0.22</v>
       </c>
       <c r="W45">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.016152431821482</v>
+        <v>2.627835677022869</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07445293414241405</v>
+        <v>0.07449698146846219</v>
       </c>
       <c r="C46">
-        <v>735.9198411306411</v>
+        <v>719.8574588276292</v>
       </c>
       <c r="D46">
-        <v>1375.023841130641</v>
+        <v>1374.027458827629</v>
       </c>
       <c r="E46">
-        <v>226.104</v>
+        <v>241.1700000000001</v>
       </c>
       <c r="F46">
-        <v>662.904</v>
+        <v>677.97</v>
       </c>
       <c r="G46">
         <v>23.8</v>
@@ -5053,28 +5053,28 @@
         <v>125.25</v>
       </c>
       <c r="M46">
-        <v>47.6627976</v>
+        <v>48.74604300000001</v>
       </c>
       <c r="N46">
-        <v>77.5872024</v>
+        <v>76.50395699999999</v>
       </c>
       <c r="O46">
-        <v>17.069184528</v>
+        <v>16.83087054</v>
       </c>
       <c r="P46">
-        <v>60.518017872</v>
+        <v>59.67308645999999</v>
       </c>
       <c r="Q46">
-        <v>129.518017872</v>
+        <v>128.67308646</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08888723954002507</v>
+        <v>0.08956378448811307</v>
       </c>
       <c r="T46">
-        <v>0.9950863635109718</v>
+        <v>1.010710958155036</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.627835677022869</v>
+        <v>2.569439328644583</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07449698146846219</v>
+        <v>0.07454102879451034</v>
       </c>
       <c r="C47">
-        <v>719.8574588276292</v>
+        <v>703.7965194942434</v>
       </c>
       <c r="D47">
-        <v>1374.027458827629</v>
+        <v>1373.032519494243</v>
       </c>
       <c r="E47">
-        <v>241.1700000000001</v>
+        <v>256.236</v>
       </c>
       <c r="F47">
-        <v>677.97</v>
+        <v>693.0359999999999</v>
       </c>
       <c r="G47">
         <v>23.8</v>
@@ -5135,28 +5135,28 @@
         <v>125.25</v>
       </c>
       <c r="M47">
-        <v>48.74604300000001</v>
+        <v>49.8292884</v>
       </c>
       <c r="N47">
-        <v>76.50395699999999</v>
+        <v>75.4207116</v>
       </c>
       <c r="O47">
-        <v>16.83087054</v>
+        <v>16.592556552</v>
       </c>
       <c r="P47">
-        <v>59.67308645999999</v>
+        <v>58.828155048</v>
       </c>
       <c r="Q47">
-        <v>128.67308646</v>
+        <v>127.828155048</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08956378448811307</v>
+        <v>0.09026538665650062</v>
       </c>
       <c r="T47">
-        <v>1.010710958155036</v>
+        <v>1.026914241489622</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.569439328644583</v>
+        <v>2.513581951934919</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07454102879451034</v>
+        <v>0.07601481612055849</v>
       </c>
       <c r="C48">
-        <v>703.7965194942434</v>
+        <v>656.2516680954922</v>
       </c>
       <c r="D48">
-        <v>1373.032519494243</v>
+        <v>1340.553668095492</v>
       </c>
       <c r="E48">
-        <v>256.236</v>
+        <v>271.302</v>
       </c>
       <c r="F48">
-        <v>693.0359999999999</v>
+        <v>708.102</v>
       </c>
       <c r="G48">
         <v>23.8</v>
@@ -5217,45 +5217,45 @@
         <v>125.25</v>
       </c>
       <c r="M48">
-        <v>49.8292884</v>
+        <v>53.6741316</v>
       </c>
       <c r="N48">
-        <v>75.4207116</v>
+        <v>71.57586839999999</v>
       </c>
       <c r="O48">
-        <v>16.592556552</v>
+        <v>15.746691048</v>
       </c>
       <c r="P48">
-        <v>58.828155048</v>
+        <v>55.82917735199999</v>
       </c>
       <c r="Q48">
-        <v>127.828155048</v>
+        <v>124.829177352</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09026538665650062</v>
+        <v>0.09099346437841224</v>
       </c>
       <c r="T48">
-        <v>1.026914241489622</v>
+        <v>1.043728969478343</v>
       </c>
       <c r="U48">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V48">
         <v>0.22</v>
       </c>
       <c r="W48">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.513581951934919</v>
+        <v>2.333526342510961</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07601481612055849</v>
+        <v>0.07608928344660665</v>
       </c>
       <c r="C49">
-        <v>656.2516680954922</v>
+        <v>639.5853135220178</v>
       </c>
       <c r="D49">
-        <v>1340.553668095492</v>
+        <v>1338.953313522018</v>
       </c>
       <c r="E49">
-        <v>271.302</v>
+        <v>286.3680000000001</v>
       </c>
       <c r="F49">
-        <v>708.102</v>
+        <v>723.168</v>
       </c>
       <c r="G49">
         <v>23.8</v>
@@ -5299,28 +5299,28 @@
         <v>125.25</v>
       </c>
       <c r="M49">
-        <v>53.6741316</v>
+        <v>54.8161344</v>
       </c>
       <c r="N49">
-        <v>71.57586839999999</v>
+        <v>70.43386559999999</v>
       </c>
       <c r="O49">
-        <v>15.746691048</v>
+        <v>15.495450432</v>
       </c>
       <c r="P49">
-        <v>55.82917735199999</v>
+        <v>54.93841516799999</v>
       </c>
       <c r="Q49">
-        <v>124.829177352</v>
+        <v>123.938415168</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09099346437841224</v>
+        <v>0.09174954508962815</v>
       </c>
       <c r="T49">
-        <v>1.043728969478343</v>
+        <v>1.061190417774323</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.333526342510961</v>
+        <v>2.284911210375316</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07608928344660665</v>
+        <v>0.0761637507726548</v>
       </c>
       <c r="C50">
-        <v>639.5853135220179</v>
+        <v>622.9227754028661</v>
       </c>
       <c r="D50">
-        <v>1338.953313522018</v>
+        <v>1337.356775402866</v>
       </c>
       <c r="E50">
-        <v>286.3679999999999</v>
+        <v>301.434</v>
       </c>
       <c r="F50">
-        <v>723.1679999999999</v>
+        <v>738.2339999999999</v>
       </c>
       <c r="G50">
         <v>23.8</v>
@@ -5381,28 +5381,28 @@
         <v>125.25</v>
       </c>
       <c r="M50">
-        <v>54.8161344</v>
+        <v>55.9581372</v>
       </c>
       <c r="N50">
-        <v>70.4338656</v>
+        <v>69.2918628</v>
       </c>
       <c r="O50">
-        <v>15.495450432</v>
+        <v>15.244209816</v>
       </c>
       <c r="P50">
-        <v>54.93841516800001</v>
+        <v>54.047652984</v>
       </c>
       <c r="Q50">
-        <v>123.938415168</v>
+        <v>123.047652984</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09174954508962815</v>
+        <v>0.09253527602481332</v>
       </c>
       <c r="T50">
-        <v>1.061190417774322</v>
+        <v>1.079336628748575</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.284911210375316</v>
+        <v>2.238280369347248</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0761637507726548</v>
+        <v>0.07623821809870295</v>
       </c>
       <c r="C51">
-        <v>622.9227754028661</v>
+        <v>606.2640401023314</v>
       </c>
       <c r="D51">
-        <v>1337.356775402866</v>
+        <v>1335.764040102331</v>
       </c>
       <c r="E51">
-        <v>301.434</v>
+        <v>316.5</v>
       </c>
       <c r="F51">
-        <v>738.2339999999999</v>
+        <v>753.3</v>
       </c>
       <c r="G51">
         <v>23.8</v>
@@ -5463,28 +5463,28 @@
         <v>125.25</v>
       </c>
       <c r="M51">
-        <v>55.9581372</v>
+        <v>57.10014</v>
       </c>
       <c r="N51">
-        <v>69.2918628</v>
+        <v>68.14985999999999</v>
       </c>
       <c r="O51">
-        <v>15.244209816</v>
+        <v>14.9929692</v>
       </c>
       <c r="P51">
-        <v>54.047652984</v>
+        <v>53.15689079999999</v>
       </c>
       <c r="Q51">
-        <v>123.047652984</v>
+        <v>122.1568908</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09253527602481332</v>
+        <v>0.09335243619740588</v>
       </c>
       <c r="T51">
-        <v>1.079336628748575</v>
+        <v>1.098208688161799</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.238280369347248</v>
+        <v>2.193514761960303</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07623821809870295</v>
+        <v>0.07631268542475109</v>
       </c>
       <c r="C52">
-        <v>606.2640401023314</v>
+        <v>589.6090940495869</v>
       </c>
       <c r="D52">
-        <v>1335.764040102331</v>
+        <v>1334.175094049587</v>
       </c>
       <c r="E52">
-        <v>316.5</v>
+        <v>331.566</v>
       </c>
       <c r="F52">
-        <v>753.3</v>
+        <v>768.366</v>
       </c>
       <c r="G52">
         <v>23.8</v>
@@ -5545,28 +5545,28 @@
         <v>125.25</v>
       </c>
       <c r="M52">
-        <v>57.10014</v>
+        <v>58.2421428</v>
       </c>
       <c r="N52">
-        <v>68.14985999999999</v>
+        <v>67.00785719999999</v>
       </c>
       <c r="O52">
-        <v>14.9929692</v>
+        <v>14.741728584</v>
       </c>
       <c r="P52">
-        <v>53.15689079999999</v>
+        <v>52.26612861599999</v>
       </c>
       <c r="Q52">
-        <v>122.1568908</v>
+        <v>121.266128616</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09335243619740588</v>
+        <v>0.09420294984643079</v>
       </c>
       <c r="T52">
-        <v>1.098208688161799</v>
+        <v>1.117851035714337</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.193514761960303</v>
+        <v>2.150504668588533</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07631268542475109</v>
+        <v>0.07638715275079924</v>
       </c>
       <c r="C53">
-        <v>589.6090940495869</v>
+        <v>572.9579237383025</v>
       </c>
       <c r="D53">
-        <v>1334.175094049587</v>
+        <v>1332.589923738303</v>
       </c>
       <c r="E53">
-        <v>331.566</v>
+        <v>346.6320000000001</v>
       </c>
       <c r="F53">
-        <v>768.366</v>
+        <v>783.432</v>
       </c>
       <c r="G53">
         <v>23.8</v>
@@ -5627,28 +5627,28 @@
         <v>125.25</v>
       </c>
       <c r="M53">
-        <v>58.2421428</v>
+        <v>59.3841456</v>
       </c>
       <c r="N53">
-        <v>67.00785719999999</v>
+        <v>65.86585439999999</v>
       </c>
       <c r="O53">
-        <v>14.741728584</v>
+        <v>14.490487968</v>
       </c>
       <c r="P53">
-        <v>52.26612861599999</v>
+        <v>51.37536643199999</v>
       </c>
       <c r="Q53">
-        <v>121.266128616</v>
+        <v>120.375366432</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09420294984643079</v>
+        <v>0.09508890156416508</v>
       </c>
       <c r="T53">
-        <v>1.117851035714337</v>
+        <v>1.138311814414898</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.150504668588533</v>
+        <v>2.109148809577214</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07638715275079924</v>
+        <v>0.0764616200768474</v>
       </c>
       <c r="C54">
-        <v>572.9579237383025</v>
+        <v>556.3105157262614</v>
       </c>
       <c r="D54">
-        <v>1332.589923738303</v>
+        <v>1331.008515726262</v>
       </c>
       <c r="E54">
-        <v>346.6320000000001</v>
+        <v>361.6980000000001</v>
       </c>
       <c r="F54">
-        <v>783.432</v>
+        <v>798.498</v>
       </c>
       <c r="G54">
         <v>23.8</v>
@@ -5709,28 +5709,28 @@
         <v>125.25</v>
       </c>
       <c r="M54">
-        <v>59.3841456</v>
+        <v>60.52614840000001</v>
       </c>
       <c r="N54">
-        <v>65.86585439999999</v>
+        <v>64.72385159999999</v>
       </c>
       <c r="O54">
-        <v>14.490487968</v>
+        <v>14.239247352</v>
       </c>
       <c r="P54">
-        <v>51.37536643199999</v>
+        <v>50.48460424799999</v>
       </c>
       <c r="Q54">
-        <v>120.375366432</v>
+        <v>119.484604248</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09508890156416508</v>
+        <v>0.09601255335499445</v>
       </c>
       <c r="T54">
-        <v>1.138311814414898</v>
+        <v>1.159643264549526</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.109148809577214</v>
+        <v>2.069353549019154</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0764616200768474</v>
+        <v>0.07653608740289555</v>
       </c>
       <c r="C55">
-        <v>556.3105157262614</v>
+        <v>539.6668566349787</v>
       </c>
       <c r="D55">
-        <v>1331.008515726262</v>
+        <v>1329.430856634979</v>
       </c>
       <c r="E55">
-        <v>361.6980000000001</v>
+        <v>376.764</v>
       </c>
       <c r="F55">
-        <v>798.498</v>
+        <v>813.564</v>
       </c>
       <c r="G55">
         <v>23.8</v>
@@ -5791,28 +5791,28 @@
         <v>125.25</v>
       </c>
       <c r="M55">
-        <v>60.52614840000001</v>
+        <v>61.6681512</v>
       </c>
       <c r="N55">
-        <v>64.72385159999999</v>
+        <v>63.5818488</v>
       </c>
       <c r="O55">
-        <v>14.239247352</v>
+        <v>13.988006736</v>
       </c>
       <c r="P55">
-        <v>50.48460424799999</v>
+        <v>49.593842064</v>
       </c>
       <c r="Q55">
-        <v>119.484604248</v>
+        <v>118.593842064</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09601255335499445</v>
+        <v>0.09697636391933814</v>
       </c>
       <c r="T55">
-        <v>1.159643264549526</v>
+        <v>1.181902169037832</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.069353549019154</v>
+        <v>2.031032187000281</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07653608740289555</v>
+        <v>0.08270235472894369</v>
       </c>
       <c r="C56">
-        <v>539.6668566349787</v>
+        <v>405.7798760745112</v>
       </c>
       <c r="D56">
-        <v>1329.430856634979</v>
+        <v>1210.609876074511</v>
       </c>
       <c r="E56">
-        <v>376.764</v>
+        <v>391.83</v>
       </c>
       <c r="F56">
-        <v>813.564</v>
+        <v>828.63</v>
       </c>
       <c r="G56">
         <v>23.8</v>
@@ -5873,45 +5873,45 @@
         <v>125.25</v>
       </c>
       <c r="M56">
-        <v>61.6681512</v>
+        <v>74.5767</v>
       </c>
       <c r="N56">
-        <v>63.5818488</v>
+        <v>50.6733</v>
       </c>
       <c r="O56">
-        <v>13.988006736</v>
+        <v>11.148126</v>
       </c>
       <c r="P56">
-        <v>49.593842064</v>
+        <v>39.525174</v>
       </c>
       <c r="Q56">
-        <v>118.593842064</v>
+        <v>108.525174</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09697636391933814</v>
+        <v>0.09798301050876376</v>
       </c>
       <c r="T56">
-        <v>1.181902169037832</v>
+        <v>1.205150358170064</v>
       </c>
       <c r="U56">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V56">
         <v>0.22</v>
       </c>
       <c r="W56">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.031032187000281</v>
+        <v>1.679478979359505</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08270235472894369</v>
+        <v>0.08288758205499183</v>
       </c>
       <c r="C57">
-        <v>405.7798760745112</v>
+        <v>387.4723473684074</v>
       </c>
       <c r="D57">
-        <v>1210.609876074511</v>
+        <v>1207.368347368408</v>
       </c>
       <c r="E57">
-        <v>391.83</v>
+        <v>406.8960000000001</v>
       </c>
       <c r="F57">
-        <v>828.63</v>
+        <v>843.696</v>
       </c>
       <c r="G57">
         <v>23.8</v>
@@ -5955,28 +5955,28 @@
         <v>125.25</v>
       </c>
       <c r="M57">
-        <v>74.5767</v>
+        <v>75.93264000000001</v>
       </c>
       <c r="N57">
-        <v>50.6733</v>
+        <v>49.31735999999999</v>
       </c>
       <c r="O57">
-        <v>11.148126</v>
+        <v>10.8498192</v>
       </c>
       <c r="P57">
-        <v>39.525174</v>
+        <v>38.46754079999999</v>
       </c>
       <c r="Q57">
-        <v>108.525174</v>
+        <v>107.4675408</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09798301050876376</v>
+        <v>0.09903541376134509</v>
       </c>
       <c r="T57">
-        <v>1.205150358170064</v>
+        <v>1.229455283171942</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.679478979359505</v>
+        <v>1.649488283299514</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08288758205499183</v>
+        <v>0.08307280938103997</v>
       </c>
       <c r="C58">
-        <v>387.4723473684074</v>
+        <v>369.1821313388162</v>
       </c>
       <c r="D58">
-        <v>1207.368347368408</v>
+        <v>1204.144131338816</v>
       </c>
       <c r="E58">
-        <v>406.8960000000001</v>
+        <v>421.9620000000001</v>
       </c>
       <c r="F58">
-        <v>843.696</v>
+        <v>858.7620000000001</v>
       </c>
       <c r="G58">
         <v>23.8</v>
@@ -6037,28 +6037,28 @@
         <v>125.25</v>
       </c>
       <c r="M58">
-        <v>75.93264000000001</v>
+        <v>77.28858</v>
       </c>
       <c r="N58">
-        <v>49.31735999999999</v>
+        <v>47.96142</v>
       </c>
       <c r="O58">
-        <v>10.8498192</v>
+        <v>10.5515124</v>
       </c>
       <c r="P58">
-        <v>38.46754079999999</v>
+        <v>37.4099076</v>
       </c>
       <c r="Q58">
-        <v>107.4675408</v>
+        <v>106.4099076</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09903541376134509</v>
+        <v>0.1001367660024186</v>
       </c>
       <c r="T58">
-        <v>1.229455283171942</v>
+        <v>1.254890669801815</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.649488283299514</v>
+        <v>1.620549892364435</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08307280938103997</v>
+        <v>0.08325803670708815</v>
       </c>
       <c r="C59">
-        <v>369.1821313388162</v>
+        <v>350.9090896572581</v>
       </c>
       <c r="D59">
-        <v>1204.144131338816</v>
+        <v>1200.937089657258</v>
       </c>
       <c r="E59">
-        <v>421.9620000000001</v>
+        <v>437.0280000000001</v>
       </c>
       <c r="F59">
-        <v>858.7620000000001</v>
+        <v>873.8280000000001</v>
       </c>
       <c r="G59">
         <v>23.8</v>
@@ -6119,28 +6119,28 @@
         <v>125.25</v>
       </c>
       <c r="M59">
-        <v>77.28858</v>
+        <v>78.64452</v>
       </c>
       <c r="N59">
-        <v>47.96142</v>
+        <v>46.60548</v>
       </c>
       <c r="O59">
-        <v>10.5515124</v>
+        <v>10.2532056</v>
       </c>
       <c r="P59">
-        <v>37.4099076</v>
+        <v>36.3522744</v>
       </c>
       <c r="Q59">
-        <v>106.4099076</v>
+        <v>105.3522744</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1001367660024186</v>
+        <v>0.1012905635883051</v>
       </c>
       <c r="T59">
-        <v>1.254890669801815</v>
+        <v>1.281537265318825</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.620549892364435</v>
+        <v>1.592609376978841</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08325803670708815</v>
+        <v>0.08344326403313629</v>
       </c>
       <c r="C60">
-        <v>350.9090896572583</v>
+        <v>332.6530854650033</v>
       </c>
       <c r="D60">
-        <v>1200.937089657258</v>
+        <v>1197.747085465003</v>
       </c>
       <c r="E60">
-        <v>437.0279999999999</v>
+        <v>452.0939999999999</v>
       </c>
       <c r="F60">
-        <v>873.8279999999999</v>
+        <v>888.8939999999999</v>
       </c>
       <c r="G60">
         <v>23.8</v>
@@ -6201,28 +6201,28 @@
         <v>125.25</v>
       </c>
       <c r="M60">
-        <v>78.64451999999999</v>
+        <v>80.00045999999999</v>
       </c>
       <c r="N60">
-        <v>46.60548000000001</v>
+        <v>45.24954000000001</v>
       </c>
       <c r="O60">
-        <v>10.2532056</v>
+        <v>9.954898800000002</v>
       </c>
       <c r="P60">
-        <v>36.35227440000001</v>
+        <v>35.29464120000001</v>
       </c>
       <c r="Q60">
-        <v>105.3522744</v>
+        <v>104.2946412</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1012905635883051</v>
+        <v>0.1025006439832592</v>
       </c>
       <c r="T60">
-        <v>1.281537265318824</v>
+        <v>1.309483694763493</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.592609376978841</v>
+        <v>1.565615997708013</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08344326403313629</v>
+        <v>0.08362849135918443</v>
       </c>
       <c r="C61">
-        <v>332.6530854650033</v>
+        <v>314.4139833535975</v>
       </c>
       <c r="D61">
-        <v>1197.747085465003</v>
+        <v>1194.573983353597</v>
       </c>
       <c r="E61">
-        <v>452.0939999999999</v>
+        <v>467.16</v>
       </c>
       <c r="F61">
-        <v>888.8939999999999</v>
+        <v>903.9599999999999</v>
       </c>
       <c r="G61">
         <v>23.8</v>
@@ -6283,28 +6283,28 @@
         <v>125.25</v>
       </c>
       <c r="M61">
-        <v>80.00045999999999</v>
+        <v>81.35639999999999</v>
       </c>
       <c r="N61">
-        <v>45.24954000000001</v>
+        <v>43.89360000000001</v>
       </c>
       <c r="O61">
-        <v>9.954898800000002</v>
+        <v>9.656592000000002</v>
       </c>
       <c r="P61">
-        <v>35.29464120000001</v>
+        <v>34.237008</v>
       </c>
       <c r="Q61">
-        <v>104.2946412</v>
+        <v>103.237008</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1025006439832592</v>
+        <v>0.1037712283979611</v>
       </c>
       <c r="T61">
-        <v>1.309483694763493</v>
+        <v>1.338827445680395</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.565615997708013</v>
+        <v>1.539522397746213</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08362849135918443</v>
+        <v>0.08381371868523257</v>
       </c>
       <c r="C62">
-        <v>314.4139833535975</v>
+        <v>296.1916493457069</v>
       </c>
       <c r="D62">
-        <v>1194.573983353597</v>
+        <v>1191.417649345707</v>
       </c>
       <c r="E62">
-        <v>467.16</v>
+        <v>482.226</v>
       </c>
       <c r="F62">
-        <v>903.9599999999999</v>
+        <v>919.026</v>
       </c>
       <c r="G62">
         <v>23.8</v>
@@ -6365,28 +6365,28 @@
         <v>125.25</v>
       </c>
       <c r="M62">
-        <v>81.35639999999999</v>
+        <v>82.71234</v>
       </c>
       <c r="N62">
-        <v>43.89360000000001</v>
+        <v>42.53766</v>
       </c>
       <c r="O62">
-        <v>9.656592000000002</v>
+        <v>9.358285200000001</v>
       </c>
       <c r="P62">
-        <v>34.237008</v>
+        <v>33.17937480000001</v>
       </c>
       <c r="Q62">
-        <v>103.237008</v>
+        <v>102.1793748</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1037712283979611</v>
+        <v>0.1051069709877759</v>
       </c>
       <c r="T62">
-        <v>1.338827445680395</v>
+        <v>1.369676004336625</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.539522397746213</v>
+        <v>1.514284325652013</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08381371868523257</v>
+        <v>0.1135169743569065</v>
       </c>
       <c r="C63">
-        <v>296.1916493457069</v>
+        <v>-73.45198455272555</v>
       </c>
       <c r="D63">
-        <v>1191.417649345707</v>
+        <v>836.8400154472745</v>
       </c>
       <c r="E63">
-        <v>482.226</v>
+        <v>497.292</v>
       </c>
       <c r="F63">
-        <v>919.026</v>
+        <v>934.092</v>
       </c>
       <c r="G63">
         <v>23.8</v>
@@ -6447,45 +6447,45 @@
         <v>125.25</v>
       </c>
       <c r="M63">
-        <v>82.71234</v>
+        <v>137.1247056</v>
       </c>
       <c r="N63">
-        <v>42.53766</v>
+        <v>-11.8747056</v>
       </c>
       <c r="O63">
-        <v>9.358285200000001</v>
+        <v>-2.612435232</v>
       </c>
       <c r="P63">
-        <v>33.17937480000001</v>
+        <v>-9.262270367999999</v>
       </c>
       <c r="Q63">
-        <v>102.1793748</v>
+        <v>59.737729632</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1051069709877759</v>
+        <v>0.1073434222161355</v>
       </c>
       <c r="T63">
-        <v>1.369676004336625</v>
+        <v>1.42132614817865</v>
       </c>
       <c r="U63">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.22</v>
+        <v>0.20094847153495</v>
       </c>
       <c r="W63">
-        <v>0.0702</v>
+        <v>0.1173007643786693</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.514284325652013</v>
+        <v>0.9134021433406818</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1135169743569065</v>
+        <v>0.1145269743569065</v>
       </c>
       <c r="C64">
-        <v>-73.45198455272555</v>
+        <v>-96.90165612307442</v>
       </c>
       <c r="D64">
-        <v>836.8400154472745</v>
+        <v>828.4563438769255</v>
       </c>
       <c r="E64">
-        <v>497.292</v>
+        <v>512.3579999999999</v>
       </c>
       <c r="F64">
-        <v>934.092</v>
+        <v>949.1579999999999</v>
       </c>
       <c r="G64">
         <v>23.8</v>
@@ -6529,37 +6529,37 @@
         <v>125.25</v>
       </c>
       <c r="M64">
-        <v>137.1247056</v>
+        <v>139.3363944</v>
       </c>
       <c r="N64">
-        <v>-11.8747056</v>
+        <v>-14.08639439999999</v>
       </c>
       <c r="O64">
-        <v>-2.612435232</v>
+        <v>-3.099006767999998</v>
       </c>
       <c r="P64">
-        <v>-9.262270367999999</v>
+        <v>-10.98738763199999</v>
       </c>
       <c r="Q64">
-        <v>59.737729632</v>
+        <v>58.01261236800001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1073434222161355</v>
+        <v>0.1090067579517068</v>
       </c>
       <c r="T64">
-        <v>1.42132614817865</v>
+        <v>1.459740368399695</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.20094847153495</v>
+        <v>0.1977588132566175</v>
       </c>
       <c r="W64">
-        <v>0.1173007643786693</v>
+        <v>0.1177690062139286</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.9134021433406818</v>
+        <v>0.8989036966209886</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1145269743569065</v>
+        <v>0.1155369743569065</v>
       </c>
       <c r="C65">
-        <v>-96.90165612307442</v>
+        <v>-120.1850144438563</v>
       </c>
       <c r="D65">
-        <v>828.4563438769255</v>
+        <v>820.2389855561437</v>
       </c>
       <c r="E65">
-        <v>512.3579999999999</v>
+        <v>527.424</v>
       </c>
       <c r="F65">
-        <v>949.1579999999999</v>
+        <v>964.2239999999999</v>
       </c>
       <c r="G65">
         <v>23.8</v>
@@ -6611,37 +6611,37 @@
         <v>125.25</v>
       </c>
       <c r="M65">
-        <v>139.3363944</v>
+        <v>141.5480832</v>
       </c>
       <c r="N65">
-        <v>-14.08639439999999</v>
+        <v>-16.29808320000001</v>
       </c>
       <c r="O65">
-        <v>-3.099006767999998</v>
+        <v>-3.585578304000002</v>
       </c>
       <c r="P65">
-        <v>-10.98738763199999</v>
+        <v>-12.71250489600001</v>
       </c>
       <c r="Q65">
-        <v>58.01261236800001</v>
+        <v>56.28749510399999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1090067579517068</v>
+        <v>0.1107625012281431</v>
       </c>
       <c r="T65">
-        <v>1.459740368399695</v>
+        <v>1.500288711966353</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1977588132566175</v>
+        <v>0.1946688317994828</v>
       </c>
       <c r="W65">
-        <v>0.1177690062139286</v>
+        <v>0.1182226154918359</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8989036966209886</v>
+        <v>0.8848583263612855</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1155369743569065</v>
+        <v>0.1165469743569065</v>
       </c>
       <c r="C66">
-        <v>-120.1850144438563</v>
+        <v>-143.3069598324646</v>
       </c>
       <c r="D66">
-        <v>820.2389855561437</v>
+        <v>812.1830401675354</v>
       </c>
       <c r="E66">
-        <v>527.424</v>
+        <v>542.49</v>
       </c>
       <c r="F66">
-        <v>964.2239999999999</v>
+        <v>979.29</v>
       </c>
       <c r="G66">
         <v>23.8</v>
@@ -6693,37 +6693,37 @@
         <v>125.25</v>
       </c>
       <c r="M66">
-        <v>141.5480832</v>
+        <v>143.759772</v>
       </c>
       <c r="N66">
-        <v>-16.29808320000001</v>
+        <v>-18.509772</v>
       </c>
       <c r="O66">
-        <v>-3.585578304000002</v>
+        <v>-4.07214984</v>
       </c>
       <c r="P66">
-        <v>-12.71250489600001</v>
+        <v>-14.43762216</v>
       </c>
       <c r="Q66">
-        <v>56.28749510399999</v>
+        <v>54.56237784</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1107625012281431</v>
+        <v>0.1126185726918043</v>
       </c>
       <c r="T66">
-        <v>1.500288711966353</v>
+        <v>1.54315410373682</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1946688317994828</v>
+        <v>0.1916739266948754</v>
       </c>
       <c r="W66">
-        <v>0.1182226154918359</v>
+        <v>0.1186622675611923</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8848583263612855</v>
+        <v>0.8712451213403427</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1165469743569065</v>
+        <v>0.1175569743569065</v>
       </c>
       <c r="C67">
-        <v>-143.3069598324646</v>
+        <v>-166.2722019655542</v>
       </c>
       <c r="D67">
-        <v>812.1830401675354</v>
+        <v>804.2837980344458</v>
       </c>
       <c r="E67">
-        <v>542.49</v>
+        <v>557.556</v>
       </c>
       <c r="F67">
-        <v>979.29</v>
+        <v>994.356</v>
       </c>
       <c r="G67">
         <v>23.8</v>
@@ -6775,37 +6775,37 @@
         <v>125.25</v>
       </c>
       <c r="M67">
-        <v>143.759772</v>
+        <v>145.9714608</v>
       </c>
       <c r="N67">
-        <v>-18.509772</v>
+        <v>-20.72146080000002</v>
       </c>
       <c r="O67">
-        <v>-4.07214984</v>
+        <v>-4.558721376000004</v>
       </c>
       <c r="P67">
-        <v>-14.43762216</v>
+        <v>-16.16273942400001</v>
       </c>
       <c r="Q67">
-        <v>54.56237784</v>
+        <v>52.83726057599999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1126185726918043</v>
+        <v>0.1145838248297985</v>
       </c>
       <c r="T67">
-        <v>1.54315410373682</v>
+        <v>1.588540989140844</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1916739266948754</v>
+        <v>0.1887697762904076</v>
       </c>
       <c r="W67">
-        <v>0.1186622675611923</v>
+        <v>0.1190885968405682</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8712451213403427</v>
+        <v>0.8580444376836707</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1175569743569065</v>
+        <v>0.1185669743569065</v>
       </c>
       <c r="C68">
-        <v>-166.2722019655542</v>
+        <v>-189.0852690605441</v>
       </c>
       <c r="D68">
-        <v>804.2837980344458</v>
+        <v>796.536730939456</v>
       </c>
       <c r="E68">
-        <v>557.556</v>
+        <v>572.6220000000001</v>
       </c>
       <c r="F68">
-        <v>994.356</v>
+        <v>1009.422</v>
       </c>
       <c r="G68">
         <v>23.8</v>
@@ -6857,37 +6857,37 @@
         <v>125.25</v>
       </c>
       <c r="M68">
-        <v>145.9714608</v>
+        <v>148.1831496</v>
       </c>
       <c r="N68">
-        <v>-20.72146080000002</v>
+        <v>-22.93314960000001</v>
       </c>
       <c r="O68">
-        <v>-4.558721376000004</v>
+        <v>-5.045292912000002</v>
       </c>
       <c r="P68">
-        <v>-16.16273942400001</v>
+        <v>-17.88785668800001</v>
       </c>
       <c r="Q68">
-        <v>52.83726057599999</v>
+        <v>51.11214331199999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1145838248297985</v>
+        <v>0.1166681831579743</v>
       </c>
       <c r="T68">
-        <v>1.588540989140844</v>
+        <v>1.636678594872385</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1887697762904076</v>
+        <v>0.1859523169427895</v>
       </c>
       <c r="W68">
-        <v>0.1190885968405682</v>
+        <v>0.1195021998727985</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8580444376836707</v>
+        <v>0.8452378042854071</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1185669743569065</v>
+        <v>0.1195769743569065</v>
       </c>
       <c r="C69">
-        <v>-189.0852690605441</v>
+        <v>-211.7505165315478</v>
       </c>
       <c r="D69">
-        <v>796.536730939456</v>
+        <v>788.9374834684523</v>
       </c>
       <c r="E69">
-        <v>572.6220000000001</v>
+        <v>587.6880000000001</v>
       </c>
       <c r="F69">
-        <v>1009.422</v>
+        <v>1024.488</v>
       </c>
       <c r="G69">
         <v>23.8</v>
@@ -6939,37 +6939,37 @@
         <v>125.25</v>
       </c>
       <c r="M69">
-        <v>148.1831496</v>
+        <v>150.3948384</v>
       </c>
       <c r="N69">
-        <v>-22.93314960000001</v>
+        <v>-25.14483840000003</v>
       </c>
       <c r="O69">
-        <v>-5.045292912000002</v>
+        <v>-5.531864448000006</v>
       </c>
       <c r="P69">
-        <v>-17.88785668800001</v>
+        <v>-19.61297395200002</v>
       </c>
       <c r="Q69">
-        <v>51.11214331199999</v>
+        <v>49.38702604799998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1166681831579743</v>
+        <v>0.1188828138816609</v>
       </c>
       <c r="T69">
-        <v>1.636678594872385</v>
+        <v>1.687824800962147</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1859523169427895</v>
+        <v>0.183217724046572</v>
       </c>
       <c r="W69">
-        <v>0.1195021998727985</v>
+        <v>0.1199036381099632</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8452378042854071</v>
+        <v>0.8328078365753274</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1195769743569065</v>
+        <v>0.1205869743569065</v>
       </c>
       <c r="C70">
-        <v>-211.7505165315478</v>
+        <v>-234.2721351545059</v>
       </c>
       <c r="D70">
-        <v>788.9374834684523</v>
+        <v>781.4818648454942</v>
       </c>
       <c r="E70">
-        <v>587.6880000000001</v>
+        <v>602.7540000000001</v>
       </c>
       <c r="F70">
-        <v>1024.488</v>
+        <v>1039.554</v>
       </c>
       <c r="G70">
         <v>23.8</v>
@@ -7021,37 +7021,37 @@
         <v>125.25</v>
       </c>
       <c r="M70">
-        <v>150.3948384</v>
+        <v>152.6065272</v>
       </c>
       <c r="N70">
-        <v>-25.14483840000003</v>
+        <v>-27.35652720000002</v>
       </c>
       <c r="O70">
-        <v>-5.531864448000006</v>
+        <v>-6.018435984000003</v>
       </c>
       <c r="P70">
-        <v>-19.61297395200002</v>
+        <v>-21.33809121600001</v>
       </c>
       <c r="Q70">
-        <v>49.38702604799998</v>
+        <v>47.66190878399999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1188828138816609</v>
+        <v>0.1212403240068758</v>
       </c>
       <c r="T70">
-        <v>1.687824800962147</v>
+        <v>1.742270762283507</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.183217724046572</v>
+        <v>0.1805623947125638</v>
       </c>
       <c r="W70">
-        <v>0.1199036381099632</v>
+        <v>0.1202934404561957</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8328078365753274</v>
+        <v>0.8207381577843808</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1205869743569065</v>
+        <v>0.1215969743569065</v>
       </c>
       <c r="C71">
-        <v>-234.2721351545059</v>
+        <v>-256.6541587736772</v>
       </c>
       <c r="D71">
-        <v>781.4818648454942</v>
+        <v>774.165841226323</v>
       </c>
       <c r="E71">
-        <v>602.7540000000001</v>
+        <v>617.8200000000002</v>
       </c>
       <c r="F71">
-        <v>1039.554</v>
+        <v>1054.62</v>
       </c>
       <c r="G71">
         <v>23.8</v>
@@ -7103,37 +7103,37 @@
         <v>125.25</v>
       </c>
       <c r="M71">
-        <v>152.6065272</v>
+        <v>154.818216</v>
       </c>
       <c r="N71">
-        <v>-27.35652720000002</v>
+        <v>-29.56821600000004</v>
       </c>
       <c r="O71">
-        <v>-6.018435984000003</v>
+        <v>-6.505007520000007</v>
       </c>
       <c r="P71">
-        <v>-21.33809121600001</v>
+        <v>-23.06320848000003</v>
       </c>
       <c r="Q71">
-        <v>47.66190878399999</v>
+        <v>45.93679151999997</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1212403240068758</v>
+        <v>0.1237550014737717</v>
       </c>
       <c r="T71">
-        <v>1.742270762283507</v>
+        <v>1.800346454359623</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1805623947125638</v>
+        <v>0.1779829319309557</v>
       </c>
       <c r="W71">
-        <v>0.1202934404561957</v>
+        <v>0.1206721055925357</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8207381577843808</v>
+        <v>0.8090133269588895</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1215969743569065</v>
+        <v>0.1618420489242614</v>
       </c>
       <c r="C72">
-        <v>-256.6541587736772</v>
+        <v>-482.0498112010713</v>
       </c>
       <c r="D72">
-        <v>774.165841226323</v>
+        <v>563.8361887989289</v>
       </c>
       <c r="E72">
-        <v>617.8200000000002</v>
+        <v>632.8860000000002</v>
       </c>
       <c r="F72">
-        <v>1054.62</v>
+        <v>1069.686</v>
       </c>
       <c r="G72">
         <v>23.8</v>
@@ -7185,45 +7185,45 @@
         <v>125.25</v>
       </c>
       <c r="M72">
-        <v>154.818216</v>
+        <v>214.7929488</v>
       </c>
       <c r="N72">
-        <v>-29.56821600000004</v>
+        <v>-89.54294880000003</v>
       </c>
       <c r="O72">
-        <v>-6.505007520000007</v>
+        <v>-19.69944873600001</v>
       </c>
       <c r="P72">
-        <v>-23.06320848000003</v>
+        <v>-69.84350006400003</v>
       </c>
       <c r="Q72">
-        <v>45.93679151999997</v>
+        <v>-0.8435000640000254</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1237550014737717</v>
+        <v>0.1295295689982288</v>
       </c>
       <c r="T72">
-        <v>1.800346454359623</v>
+        <v>1.933708290952167</v>
       </c>
       <c r="U72">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1779829319309557</v>
+        <v>0.1282863341368681</v>
       </c>
       <c r="W72">
-        <v>0.1206721055925357</v>
+        <v>0.1750401041053169</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.8090133269588895</v>
+        <v>0.5831197006221276</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1618420489242614</v>
+        <v>0.1633920489242613</v>
       </c>
       <c r="C73">
-        <v>-482.0498112010711</v>
+        <v>-502.9545317475306</v>
       </c>
       <c r="D73">
-        <v>563.8361887989289</v>
+        <v>557.9974682524694</v>
       </c>
       <c r="E73">
-        <v>632.886</v>
+        <v>647.952</v>
       </c>
       <c r="F73">
-        <v>1069.686</v>
+        <v>1084.752</v>
       </c>
       <c r="G73">
         <v>23.8</v>
@@ -7267,37 +7267,37 @@
         <v>125.25</v>
       </c>
       <c r="M73">
-        <v>214.7929488</v>
+        <v>217.8182016</v>
       </c>
       <c r="N73">
-        <v>-89.5429488</v>
+        <v>-92.56820160000001</v>
       </c>
       <c r="O73">
-        <v>-19.699448736</v>
+        <v>-20.365004352</v>
       </c>
       <c r="P73">
-        <v>-69.84350006400001</v>
+        <v>-72.20319724800001</v>
       </c>
       <c r="Q73">
-        <v>-0.8435000640000112</v>
+        <v>-3.203197248000009</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1295295689982288</v>
+        <v>0.1325199107481655</v>
       </c>
       <c r="T73">
-        <v>1.933708290952166</v>
+        <v>2.002769301343315</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1282863341368681</v>
+        <v>0.1265045794960782</v>
       </c>
       <c r="W73">
-        <v>0.1750401041053169</v>
+        <v>0.1753978804371875</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5831197006221276</v>
+        <v>0.5750208158912649</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1633920489242613</v>
+        <v>0.1649420489242613</v>
       </c>
       <c r="C74">
-        <v>-502.9545317475306</v>
+        <v>-523.739567691209</v>
       </c>
       <c r="D74">
-        <v>557.9974682524694</v>
+        <v>552.278432308791</v>
       </c>
       <c r="E74">
-        <v>647.952</v>
+        <v>663.018</v>
       </c>
       <c r="F74">
-        <v>1084.752</v>
+        <v>1099.818</v>
       </c>
       <c r="G74">
         <v>23.8</v>
@@ -7349,37 +7349,37 @@
         <v>125.25</v>
       </c>
       <c r="M74">
-        <v>217.8182016</v>
+        <v>220.8434544</v>
       </c>
       <c r="N74">
-        <v>-92.56820160000001</v>
+        <v>-95.59345440000001</v>
       </c>
       <c r="O74">
-        <v>-20.365004352</v>
+        <v>-21.030559968</v>
       </c>
       <c r="P74">
-        <v>-72.20319724800001</v>
+        <v>-74.56289443200001</v>
       </c>
       <c r="Q74">
-        <v>-3.203197248000009</v>
+        <v>-5.562894432000007</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1325199107481655</v>
+        <v>0.1357317592943939</v>
       </c>
       <c r="T74">
-        <v>2.002769301343315</v>
+        <v>2.076945942133808</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1265045794960782</v>
+        <v>0.1247716400509265</v>
       </c>
       <c r="W74">
-        <v>0.1753978804371875</v>
+        <v>0.175745854677774</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5750208158912649</v>
+        <v>0.5671438184133022</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1649420489242613</v>
+        <v>0.1664920489242613</v>
       </c>
       <c r="C75">
-        <v>-523.739567691209</v>
+        <v>-544.4085617170737</v>
       </c>
       <c r="D75">
-        <v>552.278432308791</v>
+        <v>546.6754382829264</v>
       </c>
       <c r="E75">
-        <v>663.018</v>
+        <v>678.0840000000001</v>
       </c>
       <c r="F75">
-        <v>1099.818</v>
+        <v>1114.884</v>
       </c>
       <c r="G75">
         <v>23.8</v>
@@ -7431,37 +7431,37 @@
         <v>125.25</v>
       </c>
       <c r="M75">
-        <v>220.8434544</v>
+        <v>223.8687072</v>
       </c>
       <c r="N75">
-        <v>-95.59345440000001</v>
+        <v>-98.61870720000002</v>
       </c>
       <c r="O75">
-        <v>-21.030559968</v>
+        <v>-21.696115584</v>
       </c>
       <c r="P75">
-        <v>-74.56289443200001</v>
+        <v>-76.92259161600001</v>
       </c>
       <c r="Q75">
-        <v>-5.562894432000007</v>
+        <v>-7.922591616000005</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1357317592943939</v>
+        <v>0.139190673113409</v>
       </c>
       <c r="T75">
-        <v>2.076945942133808</v>
+        <v>2.156828478369723</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1247716400509265</v>
+        <v>0.123085536806995</v>
       </c>
       <c r="W75">
-        <v>0.175745854677774</v>
+        <v>0.1760844242091554</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5671438184133022</v>
+        <v>0.5594797127590685</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1664920489242613</v>
+        <v>0.1680420489242613</v>
       </c>
       <c r="C76">
-        <v>-544.4085617170737</v>
+        <v>-564.9650101711663</v>
       </c>
       <c r="D76">
-        <v>546.6754382829264</v>
+        <v>541.1849898288335</v>
       </c>
       <c r="E76">
-        <v>678.0840000000001</v>
+        <v>693.1499999999999</v>
       </c>
       <c r="F76">
-        <v>1114.884</v>
+        <v>1129.95</v>
       </c>
       <c r="G76">
         <v>23.8</v>
@@ -7513,37 +7513,37 @@
         <v>125.25</v>
       </c>
       <c r="M76">
-        <v>223.8687072</v>
+        <v>226.89396</v>
       </c>
       <c r="N76">
-        <v>-98.61870720000002</v>
+        <v>-101.64396</v>
       </c>
       <c r="O76">
-        <v>-21.696115584</v>
+        <v>-22.36167119999999</v>
       </c>
       <c r="P76">
-        <v>-76.92259161600001</v>
+        <v>-79.28228879999998</v>
       </c>
       <c r="Q76">
-        <v>-7.922591616000005</v>
+        <v>-10.28228879999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.139190673113409</v>
+        <v>0.1429263000379454</v>
       </c>
       <c r="T76">
-        <v>2.156828478369723</v>
+        <v>2.243101617504513</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.123085536806995</v>
+        <v>0.1214443963162351</v>
       </c>
       <c r="W76">
-        <v>0.1760844242091554</v>
+        <v>0.1764139652197</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5594797127590685</v>
+        <v>0.5520199832556143</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1680420489242613</v>
+        <v>0.1695920489242613</v>
       </c>
       <c r="C77">
-        <v>-564.9650101711663</v>
+        <v>-585.4122703361919</v>
       </c>
       <c r="D77">
-        <v>541.1849898288335</v>
+        <v>535.803729663808</v>
       </c>
       <c r="E77">
-        <v>693.1499999999999</v>
+        <v>708.2159999999999</v>
       </c>
       <c r="F77">
-        <v>1129.95</v>
+        <v>1145.016</v>
       </c>
       <c r="G77">
         <v>23.8</v>
@@ -7595,37 +7595,37 @@
         <v>125.25</v>
       </c>
       <c r="M77">
-        <v>226.89396</v>
+        <v>229.9192128</v>
       </c>
       <c r="N77">
-        <v>-101.64396</v>
+        <v>-104.6692128</v>
       </c>
       <c r="O77">
-        <v>-22.36167119999999</v>
+        <v>-23.02722681599999</v>
       </c>
       <c r="P77">
-        <v>-79.28228879999998</v>
+        <v>-81.64198598399997</v>
       </c>
       <c r="Q77">
-        <v>-10.28228879999998</v>
+        <v>-12.64198598399997</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1429263000379454</v>
+        <v>0.1469732292061931</v>
       </c>
       <c r="T77">
-        <v>2.243101617504513</v>
+        <v>2.336564184900534</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1214443963162351</v>
+        <v>0.1198464437331268</v>
       </c>
       <c r="W77">
-        <v>0.1764139652197</v>
+        <v>0.1767348340983881</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5520199832556143</v>
+        <v>0.5447565624233035</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1695920489242613</v>
+        <v>0.1711420489242613</v>
       </c>
       <c r="C78">
-        <v>-585.4122703361919</v>
+        <v>-605.7535672773118</v>
       </c>
       <c r="D78">
-        <v>535.803729663808</v>
+        <v>530.5284327226881</v>
       </c>
       <c r="E78">
-        <v>708.2159999999999</v>
+        <v>723.2819999999999</v>
       </c>
       <c r="F78">
-        <v>1145.016</v>
+        <v>1160.082</v>
       </c>
       <c r="G78">
         <v>23.8</v>
@@ -7677,37 +7677,37 @@
         <v>125.25</v>
       </c>
       <c r="M78">
-        <v>229.9192128</v>
+        <v>232.9444656</v>
       </c>
       <c r="N78">
-        <v>-104.6692128</v>
+        <v>-107.6944656</v>
       </c>
       <c r="O78">
-        <v>-23.02722681599999</v>
+        <v>-23.69278243199999</v>
       </c>
       <c r="P78">
-        <v>-81.64198598399997</v>
+        <v>-84.00168316799997</v>
       </c>
       <c r="Q78">
-        <v>-12.64198598399997</v>
+        <v>-15.00168316799997</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1469732292061931</v>
+        <v>0.1513720652586363</v>
       </c>
       <c r="T78">
-        <v>2.336564184900534</v>
+        <v>2.438153932070122</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1198464437331268</v>
+        <v>0.1182899964119174</v>
       </c>
       <c r="W78">
-        <v>0.1767348340983881</v>
+        <v>0.177047368720487</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5447565624233035</v>
+        <v>0.5376818018723515</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1711420489242613</v>
+        <v>0.1726920489242613</v>
       </c>
       <c r="C79">
-        <v>-605.7535672773118</v>
+        <v>-625.9920002874766</v>
       </c>
       <c r="D79">
-        <v>530.5284327226881</v>
+        <v>525.3559997125234</v>
       </c>
       <c r="E79">
-        <v>723.2819999999999</v>
+        <v>738.348</v>
       </c>
       <c r="F79">
-        <v>1160.082</v>
+        <v>1175.148</v>
       </c>
       <c r="G79">
         <v>23.8</v>
@@ -7759,37 +7759,37 @@
         <v>125.25</v>
       </c>
       <c r="M79">
-        <v>232.9444656</v>
+        <v>235.9697184</v>
       </c>
       <c r="N79">
-        <v>-107.6944656</v>
+        <v>-110.7197184</v>
       </c>
       <c r="O79">
-        <v>-23.69278243199999</v>
+        <v>-24.358338048</v>
       </c>
       <c r="P79">
-        <v>-84.00168316799997</v>
+        <v>-86.36138035199998</v>
       </c>
       <c r="Q79">
-        <v>-15.00168316799997</v>
+        <v>-17.36138035199998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1513720652586363</v>
+        <v>0.1561707954976652</v>
       </c>
       <c r="T79">
-        <v>2.438153932070122</v>
+        <v>2.548979110800582</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1182899964119174</v>
+        <v>0.1167734579963799</v>
       </c>
       <c r="W79">
-        <v>0.177047368720487</v>
+        <v>0.1773518896343269</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5376818018723515</v>
+        <v>0.5307884454380907</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1726920489242613</v>
+        <v>0.1742420489242613</v>
       </c>
       <c r="C80">
-        <v>-625.9920002874766</v>
+        <v>-646.1305489593623</v>
       </c>
       <c r="D80">
-        <v>525.3559997125234</v>
+        <v>520.2834510406377</v>
       </c>
       <c r="E80">
-        <v>738.348</v>
+        <v>753.414</v>
       </c>
       <c r="F80">
-        <v>1175.148</v>
+        <v>1190.214</v>
       </c>
       <c r="G80">
         <v>23.8</v>
@@ -7841,37 +7841,37 @@
         <v>125.25</v>
       </c>
       <c r="M80">
-        <v>235.9697184</v>
+        <v>238.9949712</v>
       </c>
       <c r="N80">
-        <v>-110.7197184</v>
+        <v>-113.7449712</v>
       </c>
       <c r="O80">
-        <v>-24.358338048</v>
+        <v>-25.023893664</v>
       </c>
       <c r="P80">
-        <v>-86.36138035199998</v>
+        <v>-88.72107753600001</v>
       </c>
       <c r="Q80">
-        <v>-17.36138035199998</v>
+        <v>-19.72107753600001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1561707954976652</v>
+        <v>0.1614265476642207</v>
       </c>
       <c r="T80">
-        <v>2.548979110800582</v>
+        <v>2.670359068457754</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1167734579963799</v>
+        <v>0.1152953129584511</v>
       </c>
       <c r="W80">
-        <v>0.1773518896343269</v>
+        <v>0.177648701157943</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5307884454380907</v>
+        <v>0.5240696043565958</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1742420489242613</v>
+        <v>0.1757920489242614</v>
       </c>
       <c r="C81">
-        <v>-646.1305489593623</v>
+        <v>-666.1720789089072</v>
       </c>
       <c r="D81">
-        <v>520.2834510406377</v>
+        <v>515.3079210910928</v>
       </c>
       <c r="E81">
-        <v>753.414</v>
+        <v>768.48</v>
       </c>
       <c r="F81">
-        <v>1190.214</v>
+        <v>1205.28</v>
       </c>
       <c r="G81">
         <v>23.8</v>
@@ -7923,37 +7923,37 @@
         <v>125.25</v>
       </c>
       <c r="M81">
-        <v>238.9949712</v>
+        <v>242.020224</v>
       </c>
       <c r="N81">
-        <v>-113.7449712</v>
+        <v>-116.770224</v>
       </c>
       <c r="O81">
-        <v>-25.023893664</v>
+        <v>-25.68944928</v>
       </c>
       <c r="P81">
-        <v>-88.72107753600001</v>
+        <v>-91.08077472000001</v>
       </c>
       <c r="Q81">
-        <v>-19.72107753600001</v>
+        <v>-22.08077472000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1614265476642207</v>
+        <v>0.1672078750474318</v>
       </c>
       <c r="T81">
-        <v>2.670359068457754</v>
+        <v>2.803877021880642</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1152953129584511</v>
+        <v>0.1138541215464704</v>
       </c>
       <c r="W81">
-        <v>0.177648701157943</v>
+        <v>0.1779380923934687</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5240696043565958</v>
+        <v>0.5175187343021384</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1757920489242614</v>
+        <v>0.1773420489242613</v>
       </c>
       <c r="C82">
-        <v>-666.1720789089072</v>
+        <v>-686.1193471735509</v>
       </c>
       <c r="D82">
-        <v>515.3079210910928</v>
+        <v>510.4266528264492</v>
       </c>
       <c r="E82">
-        <v>768.48</v>
+        <v>783.546</v>
       </c>
       <c r="F82">
-        <v>1205.28</v>
+        <v>1220.346</v>
       </c>
       <c r="G82">
         <v>23.8</v>
@@ -8005,37 +8005,37 @@
         <v>125.25</v>
       </c>
       <c r="M82">
-        <v>242.020224</v>
+        <v>245.0454768</v>
       </c>
       <c r="N82">
-        <v>-116.770224</v>
+        <v>-119.7954768</v>
       </c>
       <c r="O82">
-        <v>-25.68944928</v>
+        <v>-26.355004896</v>
       </c>
       <c r="P82">
-        <v>-91.08077472000001</v>
+        <v>-93.44047190400002</v>
       </c>
       <c r="Q82">
-        <v>-22.08077472000001</v>
+        <v>-24.44047190400002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1672078750474318</v>
+        <v>0.1735977632078229</v>
       </c>
       <c r="T82">
-        <v>2.803877021880642</v>
+        <v>2.951449496716465</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1138541215464704</v>
+        <v>0.1124485151076251</v>
       </c>
       <c r="W82">
-        <v>0.1779380923934687</v>
+        <v>0.1782203381663889</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5175187343021384</v>
+        <v>0.5111296141255687</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1773420489242613</v>
+        <v>0.1788920489242614</v>
       </c>
       <c r="C83">
-        <v>-686.1193471735509</v>
+        <v>-705.975007306542</v>
       </c>
       <c r="D83">
-        <v>510.4266528264492</v>
+        <v>505.6369926934581</v>
       </c>
       <c r="E83">
-        <v>783.546</v>
+        <v>798.6120000000001</v>
       </c>
       <c r="F83">
-        <v>1220.346</v>
+        <v>1235.412</v>
       </c>
       <c r="G83">
         <v>23.8</v>
@@ -8087,37 +8087,37 @@
         <v>125.25</v>
       </c>
       <c r="M83">
-        <v>245.0454768</v>
+        <v>248.0707296</v>
       </c>
       <c r="N83">
-        <v>-119.7954768</v>
+        <v>-122.8207296</v>
       </c>
       <c r="O83">
-        <v>-26.355004896</v>
+        <v>-27.02056051200001</v>
       </c>
       <c r="P83">
-        <v>-93.44047190400002</v>
+        <v>-95.80016908800002</v>
       </c>
       <c r="Q83">
-        <v>-24.44047190400002</v>
+        <v>-26.80016908800002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1735977632078229</v>
+        <v>0.1806976389415909</v>
       </c>
       <c r="T83">
-        <v>2.951449496716465</v>
+        <v>3.115418913200713</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1124485151076251</v>
+        <v>0.1110771917526541</v>
       </c>
       <c r="W83">
-        <v>0.1782203381663889</v>
+        <v>0.1784956998960671</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5111296141255687</v>
+        <v>0.5048963261484276</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1788920489242614</v>
+        <v>0.2098532223234909</v>
       </c>
       <c r="C84">
-        <v>-705.975007306542</v>
+        <v>-800.8561059508463</v>
       </c>
       <c r="D84">
-        <v>505.6369926934581</v>
+        <v>425.8218940491537</v>
       </c>
       <c r="E84">
-        <v>798.6120000000001</v>
+        <v>813.6780000000001</v>
       </c>
       <c r="F84">
-        <v>1235.412</v>
+        <v>1250.478</v>
       </c>
       <c r="G84">
         <v>23.8</v>
@@ -8169,45 +8169,45 @@
         <v>125.25</v>
       </c>
       <c r="M84">
-        <v>248.0707296</v>
+        <v>294.8627124</v>
       </c>
       <c r="N84">
-        <v>-122.8207296</v>
+        <v>-169.6127124</v>
       </c>
       <c r="O84">
-        <v>-27.02056051200001</v>
+        <v>-37.314796728</v>
       </c>
       <c r="P84">
-        <v>-95.80016908800002</v>
+        <v>-132.297915672</v>
       </c>
       <c r="Q84">
-        <v>-26.80016908800002</v>
+        <v>-63.29791567200002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1806976389415909</v>
+        <v>0.1907573435806816</v>
       </c>
       <c r="T84">
-        <v>3.115418913200713</v>
+        <v>3.347744655442993</v>
       </c>
       <c r="U84">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1110771917526541</v>
+        <v>0.09345026970592298</v>
       </c>
       <c r="W84">
-        <v>0.1784956998960671</v>
+        <v>0.2137644264033434</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.5048963261484276</v>
+        <v>0.4247739532087408</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2098532223234909</v>
+        <v>0.2117532223234909</v>
       </c>
       <c r="C85">
-        <v>-800.8561059508463</v>
+        <v>-820.0074034973943</v>
       </c>
       <c r="D85">
-        <v>425.8218940491537</v>
+        <v>421.7365965026058</v>
       </c>
       <c r="E85">
-        <v>813.6780000000001</v>
+        <v>828.7440000000001</v>
       </c>
       <c r="F85">
-        <v>1250.478</v>
+        <v>1265.544</v>
       </c>
       <c r="G85">
         <v>23.8</v>
@@ -8251,37 +8251,37 @@
         <v>125.25</v>
       </c>
       <c r="M85">
-        <v>294.8627124</v>
+        <v>298.4152752000001</v>
       </c>
       <c r="N85">
-        <v>-169.6127124</v>
+        <v>-173.1652752000001</v>
       </c>
       <c r="O85">
-        <v>-37.314796728</v>
+        <v>-38.09636054400001</v>
       </c>
       <c r="P85">
-        <v>-132.297915672</v>
+        <v>-135.068914656</v>
       </c>
       <c r="Q85">
-        <v>-63.29791567200002</v>
+        <v>-66.06891465600003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1907573435806816</v>
+        <v>0.1998171775544742</v>
       </c>
       <c r="T85">
-        <v>3.347744655442993</v>
+        <v>3.55697869640818</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09345026970592298</v>
+        <v>0.09233776649513817</v>
       </c>
       <c r="W85">
-        <v>0.2137644264033434</v>
+        <v>0.2140267546604464</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4247739532087408</v>
+        <v>0.4197171204324462</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2117532223234909</v>
+        <v>0.2136532223234908</v>
       </c>
       <c r="C86">
-        <v>-820.0074034973939</v>
+        <v>-839.0810579787866</v>
       </c>
       <c r="D86">
-        <v>421.7365965026059</v>
+        <v>417.7289420212133</v>
       </c>
       <c r="E86">
-        <v>828.7439999999999</v>
+        <v>843.8099999999999</v>
       </c>
       <c r="F86">
-        <v>1265.544</v>
+        <v>1280.61</v>
       </c>
       <c r="G86">
         <v>23.8</v>
@@ -8333,37 +8333,37 @@
         <v>125.25</v>
       </c>
       <c r="M86">
-        <v>298.4152752</v>
+        <v>301.967838</v>
       </c>
       <c r="N86">
-        <v>-173.1652752</v>
+        <v>-176.717838</v>
       </c>
       <c r="O86">
-        <v>-38.096360544</v>
+        <v>-38.87792435999999</v>
       </c>
       <c r="P86">
-        <v>-135.068914656</v>
+        <v>-137.83991364</v>
       </c>
       <c r="Q86">
-        <v>-66.068914656</v>
+        <v>-68.83991363999996</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1998171775544741</v>
+        <v>0.210084989391439</v>
       </c>
       <c r="T86">
-        <v>3.556978696408178</v>
+        <v>3.794110609502056</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09233776649513818</v>
+        <v>0.09125143983048951</v>
       </c>
       <c r="W86">
-        <v>0.2140267546604464</v>
+        <v>0.2142829104879706</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4197171204324462</v>
+        <v>0.4147792719567704</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2136532223234908</v>
+        <v>0.2155532223234909</v>
       </c>
       <c r="C87">
-        <v>-839.0810579787866</v>
+        <v>-858.0792620252994</v>
       </c>
       <c r="D87">
-        <v>417.7289420212133</v>
+        <v>413.7967379747005</v>
       </c>
       <c r="E87">
-        <v>843.8099999999999</v>
+        <v>858.876</v>
       </c>
       <c r="F87">
-        <v>1280.61</v>
+        <v>1295.676</v>
       </c>
       <c r="G87">
         <v>23.8</v>
@@ -8415,37 +8415,37 @@
         <v>125.25</v>
       </c>
       <c r="M87">
-        <v>301.967838</v>
+        <v>305.5204008</v>
       </c>
       <c r="N87">
-        <v>-176.717838</v>
+        <v>-180.2704008</v>
       </c>
       <c r="O87">
-        <v>-38.87792435999999</v>
+        <v>-39.659488176</v>
       </c>
       <c r="P87">
-        <v>-137.83991364</v>
+        <v>-140.610912624</v>
       </c>
       <c r="Q87">
-        <v>-68.83991363999996</v>
+        <v>-71.61091262400001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.210084989391439</v>
+        <v>0.2218196314908275</v>
       </c>
       <c r="T87">
-        <v>3.794110609502056</v>
+        <v>4.065118510180774</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09125143983048951</v>
+        <v>0.09019037657664659</v>
       </c>
       <c r="W87">
-        <v>0.2142829104879706</v>
+        <v>0.2145331092032267</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4147792719567704</v>
+        <v>0.4099562571665755</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2155532223234909</v>
+        <v>0.2174532223234908</v>
       </c>
       <c r="C88">
-        <v>-858.0792620252994</v>
+        <v>-877.004126477649</v>
       </c>
       <c r="D88">
-        <v>413.7967379747005</v>
+        <v>409.9378735223509</v>
       </c>
       <c r="E88">
-        <v>858.876</v>
+        <v>873.942</v>
       </c>
       <c r="F88">
-        <v>1295.676</v>
+        <v>1310.742</v>
       </c>
       <c r="G88">
         <v>23.8</v>
@@ -8497,37 +8497,37 @@
         <v>125.25</v>
       </c>
       <c r="M88">
-        <v>305.5204008</v>
+        <v>309.0729636</v>
       </c>
       <c r="N88">
-        <v>-180.2704008</v>
+        <v>-183.8229636</v>
       </c>
       <c r="O88">
-        <v>-39.659488176</v>
+        <v>-40.441051992</v>
       </c>
       <c r="P88">
-        <v>-140.610912624</v>
+        <v>-143.381911608</v>
       </c>
       <c r="Q88">
-        <v>-71.61091262400001</v>
+        <v>-74.381911608</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2218196314908275</v>
+        <v>0.2353596031439681</v>
       </c>
       <c r="T88">
-        <v>4.065118510180774</v>
+        <v>4.377819934040835</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09019037657664659</v>
+        <v>0.08915370558151273</v>
       </c>
       <c r="W88">
-        <v>0.2145331092032267</v>
+        <v>0.2147775562238793</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4099562571665755</v>
+        <v>0.4052441162796033</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2174532223234908</v>
+        <v>0.2193532223234909</v>
       </c>
       <c r="C89">
-        <v>-877.004126477649</v>
+        <v>-895.8576841654059</v>
       </c>
       <c r="D89">
-        <v>409.9378735223509</v>
+        <v>406.1503158345941</v>
       </c>
       <c r="E89">
-        <v>873.942</v>
+        <v>889.008</v>
       </c>
       <c r="F89">
-        <v>1310.742</v>
+        <v>1325.808</v>
       </c>
       <c r="G89">
         <v>23.8</v>
@@ -8579,37 +8579,37 @@
         <v>125.25</v>
       </c>
       <c r="M89">
-        <v>309.0729636</v>
+        <v>312.6255264</v>
       </c>
       <c r="N89">
-        <v>-183.8229636</v>
+        <v>-187.3755264</v>
       </c>
       <c r="O89">
-        <v>-40.441051992</v>
+        <v>-41.222615808</v>
       </c>
       <c r="P89">
-        <v>-143.381911608</v>
+        <v>-146.152910592</v>
       </c>
       <c r="Q89">
-        <v>-74.381911608</v>
+        <v>-77.15291059200001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2353596031439681</v>
+        <v>0.2511562367392988</v>
       </c>
       <c r="T89">
-        <v>4.377819934040835</v>
+        <v>4.742638261877571</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08915370558151273</v>
+        <v>0.08814059529081372</v>
       </c>
       <c r="W89">
-        <v>0.2147775562238793</v>
+        <v>0.2150164476304261</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4052441162796033</v>
+        <v>0.4006390695036987</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2193532223234909</v>
+        <v>0.2212532223234908</v>
       </c>
       <c r="C90">
-        <v>-895.8576841654059</v>
+        <v>-914.6418934778593</v>
       </c>
       <c r="D90">
-        <v>406.1503158345941</v>
+        <v>402.4321065221407</v>
       </c>
       <c r="E90">
-        <v>889.008</v>
+        <v>904.0740000000001</v>
       </c>
       <c r="F90">
-        <v>1325.808</v>
+        <v>1340.874</v>
       </c>
       <c r="G90">
         <v>23.8</v>
@@ -8661,37 +8661,37 @@
         <v>125.25</v>
       </c>
       <c r="M90">
-        <v>312.6255264</v>
+        <v>316.1780892</v>
       </c>
       <c r="N90">
-        <v>-187.3755264</v>
+        <v>-190.9280892</v>
       </c>
       <c r="O90">
-        <v>-41.222615808</v>
+        <v>-42.00417962400001</v>
       </c>
       <c r="P90">
-        <v>-146.152910592</v>
+        <v>-148.923909576</v>
       </c>
       <c r="Q90">
-        <v>-77.15291059200001</v>
+        <v>-79.92390957600003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2511562367392988</v>
+        <v>0.2698249855337805</v>
       </c>
       <c r="T90">
-        <v>4.742638261877571</v>
+        <v>5.173787194775532</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08814059529081372</v>
+        <v>0.0871502515235012</v>
       </c>
       <c r="W90">
-        <v>0.2150164476304261</v>
+        <v>0.2152499706907584</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4006390695036987</v>
+        <v>0.3961375069250054</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2212532223234908</v>
+        <v>0.2231532223234909</v>
       </c>
       <c r="C91">
-        <v>-914.6418934778593</v>
+        <v>-933.3586417405222</v>
       </c>
       <c r="D91">
-        <v>402.4321065221407</v>
+        <v>398.7813582594778</v>
       </c>
       <c r="E91">
-        <v>904.0740000000001</v>
+        <v>919.1400000000001</v>
       </c>
       <c r="F91">
-        <v>1340.874</v>
+        <v>1355.94</v>
       </c>
       <c r="G91">
         <v>23.8</v>
@@ -8743,37 +8743,37 @@
         <v>125.25</v>
       </c>
       <c r="M91">
-        <v>316.1780892</v>
+        <v>319.730652</v>
       </c>
       <c r="N91">
-        <v>-190.9280892</v>
+        <v>-194.480652</v>
       </c>
       <c r="O91">
-        <v>-42.00417962400001</v>
+        <v>-42.78574344</v>
       </c>
       <c r="P91">
-        <v>-148.923909576</v>
+        <v>-151.69490856</v>
       </c>
       <c r="Q91">
-        <v>-79.92390957600003</v>
+        <v>-82.69490856000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2698249855337805</v>
+        <v>0.2922274840871585</v>
       </c>
       <c r="T91">
-        <v>5.173787194775532</v>
+        <v>5.691165914253085</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0871502515235012</v>
+        <v>0.0861819153954623</v>
       </c>
       <c r="W91">
-        <v>0.2152499706907584</v>
+        <v>0.21547830434975</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3961375069250054</v>
+        <v>0.3917359790702831</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2231532223234909</v>
+        <v>0.2250532223234908</v>
       </c>
       <c r="C92">
-        <v>-933.3586417405222</v>
+        <v>-952.0097484095038</v>
       </c>
       <c r="D92">
-        <v>398.7813582594778</v>
+        <v>395.196251590496</v>
       </c>
       <c r="E92">
-        <v>919.1400000000001</v>
+        <v>934.2059999999999</v>
       </c>
       <c r="F92">
-        <v>1355.94</v>
+        <v>1371.006</v>
       </c>
       <c r="G92">
         <v>23.8</v>
@@ -8825,37 +8825,37 @@
         <v>125.25</v>
       </c>
       <c r="M92">
-        <v>319.730652</v>
+        <v>323.2832148</v>
       </c>
       <c r="N92">
-        <v>-194.480652</v>
+        <v>-198.0332148</v>
       </c>
       <c r="O92">
-        <v>-42.78574344</v>
+        <v>-43.567307256</v>
       </c>
       <c r="P92">
-        <v>-151.69490856</v>
+        <v>-154.465907544</v>
       </c>
       <c r="Q92">
-        <v>-82.69490856000002</v>
+        <v>-85.465907544</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2922274840871585</v>
+        <v>0.3196083156523984</v>
       </c>
       <c r="T92">
-        <v>5.691165914253085</v>
+        <v>6.32351768250343</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0861819153954623</v>
+        <v>0.08523486138012755</v>
       </c>
       <c r="W92">
-        <v>0.21547830434975</v>
+        <v>0.2157016196865659</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3917359790702831</v>
+        <v>0.3874311880914889</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2250532223234908</v>
+        <v>0.2269532223234909</v>
       </c>
       <c r="C93">
-        <v>-952.0097484095038</v>
+        <v>-970.5969680951096</v>
       </c>
       <c r="D93">
-        <v>395.196251590496</v>
+        <v>391.6750319048903</v>
       </c>
       <c r="E93">
-        <v>934.2059999999999</v>
+        <v>949.2719999999999</v>
       </c>
       <c r="F93">
-        <v>1371.006</v>
+        <v>1386.072</v>
       </c>
       <c r="G93">
         <v>23.8</v>
@@ -8907,37 +8907,37 @@
         <v>125.25</v>
       </c>
       <c r="M93">
-        <v>323.2832148</v>
+        <v>326.8357776</v>
       </c>
       <c r="N93">
-        <v>-198.0332148</v>
+        <v>-201.5857776</v>
       </c>
       <c r="O93">
-        <v>-43.567307256</v>
+        <v>-44.34887107199999</v>
       </c>
       <c r="P93">
-        <v>-154.465907544</v>
+        <v>-157.236906528</v>
       </c>
       <c r="Q93">
-        <v>-85.465907544</v>
+        <v>-88.23690652799996</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3196083156523984</v>
+        <v>0.3538343551089483</v>
       </c>
       <c r="T93">
-        <v>6.32351768250343</v>
+        <v>7.11395739281636</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08523486138012755</v>
+        <v>0.08430839549556096</v>
       </c>
       <c r="W93">
-        <v>0.2157016196865659</v>
+        <v>0.2159200803421467</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3874311880914889</v>
+        <v>0.3832199795252771</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2269532223234909</v>
+        <v>0.2288532223234908</v>
       </c>
       <c r="C94">
-        <v>-970.5969680951096</v>
+        <v>-989.1219934252256</v>
       </c>
       <c r="D94">
-        <v>391.6750319048903</v>
+        <v>388.2160065747743</v>
       </c>
       <c r="E94">
-        <v>949.2719999999999</v>
+        <v>964.338</v>
       </c>
       <c r="F94">
-        <v>1386.072</v>
+        <v>1401.138</v>
       </c>
       <c r="G94">
         <v>23.8</v>
@@ -8989,37 +8989,37 @@
         <v>125.25</v>
       </c>
       <c r="M94">
-        <v>326.8357776</v>
+        <v>330.3883404</v>
       </c>
       <c r="N94">
-        <v>-201.5857776</v>
+        <v>-205.1383404</v>
       </c>
       <c r="O94">
-        <v>-44.34887107199999</v>
+        <v>-45.130434888</v>
       </c>
       <c r="P94">
-        <v>-157.236906528</v>
+        <v>-160.007905512</v>
       </c>
       <c r="Q94">
-        <v>-88.23690652799996</v>
+        <v>-91.00790551200001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3538343551089483</v>
+        <v>0.3978392629816553</v>
       </c>
       <c r="T94">
-        <v>7.11395739281636</v>
+        <v>8.130237020361555</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08430839549556096</v>
+        <v>0.08340185360851191</v>
       </c>
       <c r="W94">
-        <v>0.2159200803421467</v>
+        <v>0.2161338429191129</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3832199795252771</v>
+        <v>0.379099334584145</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2288532223234908</v>
+        <v>0.2307532223234909</v>
       </c>
       <c r="C95">
-        <v>-989.1219934252256</v>
+        <v>-1007.586457758306</v>
       </c>
       <c r="D95">
-        <v>388.2160065747743</v>
+        <v>384.8175422416937</v>
       </c>
       <c r="E95">
-        <v>964.338</v>
+        <v>979.404</v>
       </c>
       <c r="F95">
-        <v>1401.138</v>
+        <v>1416.204</v>
       </c>
       <c r="G95">
         <v>23.8</v>
@@ -9071,37 +9071,37 @@
         <v>125.25</v>
       </c>
       <c r="M95">
-        <v>330.3883404</v>
+        <v>333.9409032</v>
       </c>
       <c r="N95">
-        <v>-205.1383404</v>
+        <v>-208.6909032</v>
       </c>
       <c r="O95">
-        <v>-45.130434888</v>
+        <v>-45.911998704</v>
       </c>
       <c r="P95">
-        <v>-160.007905512</v>
+        <v>-162.778904496</v>
       </c>
       <c r="Q95">
-        <v>-91.00790551200001</v>
+        <v>-93.778904496</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3978392629816553</v>
+        <v>0.4565124734785979</v>
       </c>
       <c r="T95">
-        <v>8.130237020361555</v>
+        <v>9.48527652375515</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08340185360851191</v>
+        <v>0.08251459984671923</v>
       </c>
       <c r="W95">
-        <v>0.2161338429191129</v>
+        <v>0.2163430573561436</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.379099334584145</v>
+        <v>0.3750663629396329</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2307532223234909</v>
+        <v>0.2326532223234909</v>
       </c>
       <c r="C96">
-        <v>-1007.586457758306</v>
+        <v>-1025.991937755101</v>
       </c>
       <c r="D96">
-        <v>384.8175422416937</v>
+        <v>381.4780622448991</v>
       </c>
       <c r="E96">
-        <v>979.404</v>
+        <v>994.47</v>
       </c>
       <c r="F96">
-        <v>1416.204</v>
+        <v>1431.27</v>
       </c>
       <c r="G96">
         <v>23.8</v>
@@ -9153,37 +9153,37 @@
         <v>125.25</v>
       </c>
       <c r="M96">
-        <v>333.9409032</v>
+        <v>337.493466</v>
       </c>
       <c r="N96">
-        <v>-208.6909032</v>
+        <v>-212.243466</v>
       </c>
       <c r="O96">
-        <v>-45.911998704</v>
+        <v>-46.69356252</v>
       </c>
       <c r="P96">
-        <v>-162.778904496</v>
+        <v>-165.54990348</v>
       </c>
       <c r="Q96">
-        <v>-93.778904496</v>
+        <v>-96.54990348000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4565124734785979</v>
+        <v>0.5386549681743178</v>
       </c>
       <c r="T96">
-        <v>9.48527652375515</v>
+        <v>11.38233182850619</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08251459984671923</v>
+        <v>0.08164602511149059</v>
       </c>
       <c r="W96">
-        <v>0.2163430573561436</v>
+        <v>0.2165478672787105</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3750663629396329</v>
+        <v>0.371118295961321</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2326532223234909</v>
+        <v>0.2345532223234909</v>
       </c>
       <c r="C97">
-        <v>-1025.991937755101</v>
+        <v>-1044.339955817626</v>
       </c>
       <c r="D97">
-        <v>381.4780622448991</v>
+        <v>378.1960441823739</v>
       </c>
       <c r="E97">
-        <v>994.47</v>
+        <v>1009.536</v>
       </c>
       <c r="F97">
-        <v>1431.27</v>
+        <v>1446.336</v>
       </c>
       <c r="G97">
         <v>23.8</v>
@@ -9235,37 +9235,37 @@
         <v>125.25</v>
       </c>
       <c r="M97">
-        <v>337.493466</v>
+        <v>341.0460288</v>
       </c>
       <c r="N97">
-        <v>-212.243466</v>
+        <v>-215.7960288</v>
       </c>
       <c r="O97">
-        <v>-46.69356252</v>
+        <v>-47.47512633600001</v>
       </c>
       <c r="P97">
-        <v>-165.54990348</v>
+        <v>-168.320902464</v>
       </c>
       <c r="Q97">
-        <v>-96.54990348000001</v>
+        <v>-99.32090246400003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5386549681743178</v>
+        <v>0.6618687102178974</v>
       </c>
       <c r="T97">
-        <v>11.38233182850619</v>
+        <v>14.22791478563274</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08164602511149059</v>
+        <v>0.08079554568324589</v>
       </c>
       <c r="W97">
-        <v>0.2165478672787105</v>
+        <v>0.2167484103278906</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.371118295961321</v>
+        <v>0.3672524803783904</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2345532223234909</v>
+        <v>0.2364532223234909</v>
       </c>
       <c r="C98">
-        <v>-1044.339955817626</v>
+        <v>-1062.631982403311</v>
       </c>
       <c r="D98">
-        <v>378.1960441823739</v>
+        <v>374.9700175966883</v>
       </c>
       <c r="E98">
-        <v>1009.536</v>
+        <v>1024.602</v>
       </c>
       <c r="F98">
-        <v>1446.336</v>
+        <v>1461.402</v>
       </c>
       <c r="G98">
         <v>23.8</v>
@@ -9317,37 +9317,37 @@
         <v>125.25</v>
       </c>
       <c r="M98">
-        <v>341.0460288</v>
+        <v>344.5985916</v>
       </c>
       <c r="N98">
-        <v>-215.7960288</v>
+        <v>-219.3485916</v>
       </c>
       <c r="O98">
-        <v>-47.475126336</v>
+        <v>-48.25669015199999</v>
       </c>
       <c r="P98">
-        <v>-168.320902464</v>
+        <v>-171.091901448</v>
       </c>
       <c r="Q98">
-        <v>-99.320902464</v>
+        <v>-102.091901448</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6618687102178957</v>
+        <v>0.8672249469571945</v>
       </c>
       <c r="T98">
-        <v>14.2279147856327</v>
+        <v>18.97055304751027</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08079554568324591</v>
+        <v>0.07996260191331554</v>
       </c>
       <c r="W98">
-        <v>0.2167484103278906</v>
+        <v>0.2169448184688402</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3672524803783905</v>
+        <v>0.3634663723332525</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2364532223234909</v>
+        <v>0.2383532223234908</v>
       </c>
       <c r="C99">
-        <v>-1062.631982403311</v>
+        <v>-1080.869438221707</v>
       </c>
       <c r="D99">
-        <v>374.9700175966883</v>
+        <v>371.7985617782929</v>
       </c>
       <c r="E99">
-        <v>1024.602</v>
+        <v>1039.668</v>
       </c>
       <c r="F99">
-        <v>1461.402</v>
+        <v>1476.468</v>
       </c>
       <c r="G99">
         <v>23.8</v>
@@ -9399,37 +9399,37 @@
         <v>125.25</v>
       </c>
       <c r="M99">
-        <v>344.5985916</v>
+        <v>348.1511544</v>
       </c>
       <c r="N99">
-        <v>-219.3485916</v>
+        <v>-222.9011544</v>
       </c>
       <c r="O99">
-        <v>-48.25669015199999</v>
+        <v>-49.038253968</v>
       </c>
       <c r="P99">
-        <v>-171.091901448</v>
+        <v>-173.862900432</v>
       </c>
       <c r="Q99">
-        <v>-102.091901448</v>
+        <v>-104.862900432</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8672249469571945</v>
+        <v>1.277937420435792</v>
       </c>
       <c r="T99">
-        <v>18.97055304751027</v>
+        <v>28.4558295712654</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07996260191331554</v>
+        <v>0.07914665699583273</v>
       </c>
       <c r="W99">
-        <v>0.2169448184688402</v>
+        <v>0.2171372182803826</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3634663723332525</v>
+        <v>0.3597575317992396</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2383532223234908</v>
+        <v>0.2402532223234908</v>
       </c>
       <c r="C100">
-        <v>-1080.869438221707</v>
+        <v>-1099.05369632065</v>
       </c>
       <c r="D100">
-        <v>371.7985617782929</v>
+        <v>368.6803036793495</v>
       </c>
       <c r="E100">
-        <v>1039.668</v>
+        <v>1054.734</v>
       </c>
       <c r="F100">
-        <v>1476.468</v>
+        <v>1491.534</v>
       </c>
       <c r="G100">
         <v>23.8</v>
@@ -9481,37 +9481,37 @@
         <v>125.25</v>
       </c>
       <c r="M100">
-        <v>348.1511544</v>
+        <v>351.7037172</v>
       </c>
       <c r="N100">
-        <v>-222.9011544</v>
+        <v>-226.4537172</v>
       </c>
       <c r="O100">
-        <v>-49.038253968</v>
+        <v>-49.81981778399999</v>
       </c>
       <c r="P100">
-        <v>-173.862900432</v>
+        <v>-176.633899416</v>
       </c>
       <c r="Q100">
-        <v>-104.862900432</v>
+        <v>-107.633899416</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.277937420435792</v>
+        <v>2.510074840871583</v>
       </c>
       <c r="T100">
-        <v>28.4558295712654</v>
+        <v>56.9116591425308</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07914665699583273</v>
+        <v>0.07834719581405665</v>
       </c>
       <c r="W100">
-        <v>0.2171372182803826</v>
+        <v>0.2173257312270454</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3597575317992396</v>
+        <v>0.3561236173366211</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2402532223234908</v>
-      </c>
-      <c r="C101">
-        <v>-1099.05369632065</v>
-      </c>
-      <c r="D101">
-        <v>368.6803036793495</v>
-      </c>
-      <c r="E101">
-        <v>1054.734</v>
-      </c>
-      <c r="F101">
-        <v>1491.534</v>
-      </c>
-      <c r="G101">
-        <v>23.8</v>
-      </c>
-      <c r="H101">
-        <v>1069.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>194.25</v>
-      </c>
-      <c r="K101">
-        <v>69</v>
-      </c>
-      <c r="L101">
-        <v>125.25</v>
-      </c>
-      <c r="M101">
-        <v>351.7037172</v>
-      </c>
-      <c r="N101">
-        <v>-226.4537172</v>
-      </c>
-      <c r="O101">
-        <v>-49.81981778399999</v>
-      </c>
-      <c r="P101">
-        <v>-176.633899416</v>
-      </c>
-      <c r="Q101">
-        <v>-107.633899416</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.510074840871583</v>
-      </c>
-      <c r="T101">
-        <v>56.9116591425308</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07834719581405665</v>
-      </c>
-      <c r="W101">
-        <v>0.2173257312270454</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3561236173366211</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
